--- a/research/traditional_assets/database/data/denmark/denmark_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_software_entertainment.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.104434679691828</v>
+        <v>0.104240023396506</v>
       </c>
       <c r="C2">
-        <v>916.443715189654</v>
+        <v>909.1803923779767</v>
       </c>
       <c r="D2">
-        <v>867.8437151896539</v>
+        <v>870.7343923779766</v>
       </c>
       <c r="E2">
-        <v>-391.5</v>
+        <v>-381.346</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.154</v>
       </c>
       <c r="G2">
         <v>48.6</v>
@@ -1457,28 +1457,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5107461999999999</v>
       </c>
       <c r="N2">
-        <v>75.12857142857143</v>
+        <v>74.61782522857143</v>
       </c>
       <c r="O2">
-        <v>16.52828571428572</v>
+        <v>16.41592155028572</v>
       </c>
       <c r="P2">
-        <v>58.60028571428572</v>
+        <v>58.20190367828572</v>
       </c>
       <c r="Q2">
-        <v>104.9002857142857</v>
+        <v>104.5019036782857</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.104434679691828</v>
+        <v>0.1048966498954606</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.364818704283155</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>147.0957031664092</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.104240023396506</v>
+        <v>0.1040453671011839</v>
       </c>
       <c r="C3">
-        <v>909.1803923779767</v>
+        <v>901.9363908802667</v>
       </c>
       <c r="D3">
-        <v>870.7343923779766</v>
+        <v>873.6443908802667</v>
       </c>
       <c r="E3">
-        <v>-381.346</v>
+        <v>-371.192</v>
       </c>
       <c r="F3">
-        <v>10.154</v>
+        <v>20.308</v>
       </c>
       <c r="G3">
         <v>48.6</v>
@@ -1539,28 +1539,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M3">
-        <v>0.5107461999999999</v>
+        <v>1.0214924</v>
       </c>
       <c r="N3">
-        <v>74.61782522857143</v>
+        <v>74.10707902857143</v>
       </c>
       <c r="O3">
-        <v>16.41592155028572</v>
+        <v>16.30355738628571</v>
       </c>
       <c r="P3">
-        <v>58.20190367828572</v>
+        <v>57.80352164228572</v>
       </c>
       <c r="Q3">
-        <v>104.5019036782857</v>
+        <v>104.1035216422857</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1048966498954606</v>
+        <v>0.1053680480624326</v>
       </c>
       <c r="T3">
-        <v>1.364818704283155</v>
+        <v>1.375705497977659</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>147.0957031664092</v>
+        <v>73.54785158320458</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1040453671011839</v>
+        <v>0.1038507108058619</v>
       </c>
       <c r="C4">
-        <v>901.9363908802667</v>
+        <v>894.7119050618647</v>
       </c>
       <c r="D4">
-        <v>873.6443908802667</v>
+        <v>876.5739050618647</v>
       </c>
       <c r="E4">
-        <v>-371.192</v>
+        <v>-361.038</v>
       </c>
       <c r="F4">
-        <v>20.308</v>
+        <v>30.462</v>
       </c>
       <c r="G4">
         <v>48.6</v>
@@ -1621,28 +1621,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M4">
-        <v>1.0214924</v>
+        <v>1.5322386</v>
       </c>
       <c r="N4">
-        <v>74.10707902857143</v>
+        <v>73.59633282857143</v>
       </c>
       <c r="O4">
-        <v>16.30355738628571</v>
+        <v>16.19119322228572</v>
       </c>
       <c r="P4">
-        <v>57.80352164228572</v>
+        <v>57.40513960628572</v>
       </c>
       <c r="Q4">
-        <v>104.1035216422857</v>
+        <v>103.7051396062857</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1053680480624326</v>
+        <v>0.1058491657792391</v>
       </c>
       <c r="T4">
-        <v>1.375705497977659</v>
+        <v>1.386816761645246</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.54785158320458</v>
+        <v>49.03190105546972</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1038507108058619</v>
+        <v>0.1036560545105399</v>
       </c>
       <c r="C5">
-        <v>894.7119050618647</v>
+        <v>887.5071319038749</v>
       </c>
       <c r="D5">
-        <v>876.5739050618647</v>
+        <v>879.5231319038749</v>
       </c>
       <c r="E5">
-        <v>-361.038</v>
+        <v>-350.884</v>
       </c>
       <c r="F5">
-        <v>30.462</v>
+        <v>40.616</v>
       </c>
       <c r="G5">
         <v>48.6</v>
@@ -1703,28 +1703,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M5">
-        <v>1.5322386</v>
+        <v>2.0429848</v>
       </c>
       <c r="N5">
-        <v>73.59633282857143</v>
+        <v>73.08558662857143</v>
       </c>
       <c r="O5">
-        <v>16.19119322228572</v>
+        <v>16.07882905828572</v>
       </c>
       <c r="P5">
-        <v>57.40513960628572</v>
+        <v>57.00675757028571</v>
       </c>
       <c r="Q5">
-        <v>103.7051396062857</v>
+        <v>103.3067575702857</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1058491657792391</v>
+        <v>0.1063403067818124</v>
       </c>
       <c r="T5">
-        <v>1.386816761645246</v>
+        <v>1.398159509972573</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.03190105546972</v>
+        <v>36.77392579160229</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1036560545105399</v>
+        <v>0.1034613982152179</v>
       </c>
       <c r="C6">
-        <v>887.5071319038749</v>
+        <v>880.3222710473175</v>
       </c>
       <c r="D6">
-        <v>879.5231319038749</v>
+        <v>882.4922710473174</v>
       </c>
       <c r="E6">
-        <v>-350.884</v>
+        <v>-340.73</v>
       </c>
       <c r="F6">
-        <v>40.616</v>
+        <v>50.77</v>
       </c>
       <c r="G6">
         <v>48.6</v>
@@ -1785,28 +1785,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M6">
-        <v>2.0429848</v>
+        <v>2.553731</v>
       </c>
       <c r="N6">
-        <v>73.08558662857143</v>
+        <v>72.57484042857143</v>
       </c>
       <c r="O6">
-        <v>16.07882905828572</v>
+        <v>15.96646489428572</v>
       </c>
       <c r="P6">
-        <v>57.00675757028571</v>
+        <v>56.60837553428572</v>
       </c>
       <c r="Q6">
-        <v>103.3067575702857</v>
+        <v>102.9083755342857</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1063403067818124</v>
+        <v>0.1068417875949662</v>
       </c>
       <c r="T6">
-        <v>1.398159509972573</v>
+        <v>1.40974105300153</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.77392579160229</v>
+        <v>29.41914063328183</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1034613982152179</v>
+        <v>0.1032667419198959</v>
       </c>
       <c r="C7">
-        <v>880.3222710473175</v>
+        <v>873.157524838177</v>
       </c>
       <c r="D7">
-        <v>882.4922710473174</v>
+        <v>885.4815248381769</v>
       </c>
       <c r="E7">
-        <v>-340.73</v>
+        <v>-330.576</v>
       </c>
       <c r="F7">
-        <v>50.77</v>
+        <v>60.92400000000001</v>
       </c>
       <c r="G7">
         <v>48.6</v>
@@ -1867,28 +1867,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M7">
-        <v>2.553731</v>
+        <v>3.0644772</v>
       </c>
       <c r="N7">
-        <v>72.57484042857143</v>
+        <v>72.06409422857143</v>
       </c>
       <c r="O7">
-        <v>15.96646489428572</v>
+        <v>15.85410073028572</v>
       </c>
       <c r="P7">
-        <v>56.60837553428572</v>
+        <v>56.20999349828572</v>
       </c>
       <c r="Q7">
-        <v>102.9083755342857</v>
+        <v>102.5099934982857</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1068417875949662</v>
+        <v>0.1073539382126552</v>
       </c>
       <c r="T7">
-        <v>1.40974105300153</v>
+        <v>1.421569011839612</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.41914063328183</v>
+        <v>24.51595052773486</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1032667419198959</v>
+        <v>0.1030720856245739</v>
       </c>
       <c r="C8">
-        <v>873.157524838177</v>
+        <v>866.0130983733708</v>
       </c>
       <c r="D8">
-        <v>885.4815248381769</v>
+        <v>888.4910983733707</v>
       </c>
       <c r="E8">
-        <v>-330.576</v>
+        <v>-320.422</v>
       </c>
       <c r="F8">
-        <v>60.924</v>
+        <v>71.07799999999999</v>
       </c>
       <c r="G8">
         <v>48.6</v>
@@ -1949,28 +1949,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M8">
-        <v>3.0644772</v>
+        <v>3.575223399999999</v>
       </c>
       <c r="N8">
-        <v>72.06409422857143</v>
+        <v>71.55334802857143</v>
       </c>
       <c r="O8">
-        <v>15.85410073028572</v>
+        <v>15.74173656628572</v>
       </c>
       <c r="P8">
-        <v>56.20999349828572</v>
+        <v>55.81161146228572</v>
       </c>
       <c r="Q8">
-        <v>102.5099934982857</v>
+        <v>102.1116114622857</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1073539382126552</v>
+        <v>0.1078771028221224</v>
       </c>
       <c r="T8">
-        <v>1.421569011839612</v>
+        <v>1.43365133538389</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.51595052773486</v>
+        <v>21.0136718809156</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1030720856245739</v>
+        <v>0.1028774293292518</v>
       </c>
       <c r="C9">
-        <v>866.013098373371</v>
+        <v>858.88919954766</v>
       </c>
       <c r="D9">
-        <v>888.491098373371</v>
+        <v>891.52119954766</v>
       </c>
       <c r="E9">
-        <v>-320.422</v>
+        <v>-310.268</v>
       </c>
       <c r="F9">
-        <v>71.078</v>
+        <v>81.232</v>
       </c>
       <c r="G9">
         <v>48.6</v>
@@ -2031,28 +2031,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M9">
-        <v>3.5752234</v>
+        <v>4.085969599999999</v>
       </c>
       <c r="N9">
-        <v>71.55334802857143</v>
+        <v>71.04260182857143</v>
       </c>
       <c r="O9">
-        <v>15.74173656628572</v>
+        <v>15.62937240228572</v>
       </c>
       <c r="P9">
-        <v>55.81161146228572</v>
+        <v>55.41322942628572</v>
       </c>
       <c r="Q9">
-        <v>102.1116114622857</v>
+        <v>101.7132294262857</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1078771028221224</v>
+        <v>0.1084116405752737</v>
       </c>
       <c r="T9">
-        <v>1.43365133538389</v>
+        <v>1.445996318135652</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.01367188091559</v>
+        <v>18.38696289580114</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1028774293292518</v>
+        <v>0.1026827730339298</v>
       </c>
       <c r="C10">
-        <v>858.88919954766</v>
+        <v>851.7860391015172</v>
       </c>
       <c r="D10">
-        <v>891.52119954766</v>
+        <v>894.5720391015171</v>
       </c>
       <c r="E10">
-        <v>-310.268</v>
+        <v>-300.114</v>
       </c>
       <c r="F10">
-        <v>81.232</v>
+        <v>91.386</v>
       </c>
       <c r="G10">
         <v>48.6</v>
@@ -2113,28 +2113,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M10">
-        <v>4.085969599999999</v>
+        <v>4.596715799999999</v>
       </c>
       <c r="N10">
-        <v>71.04260182857143</v>
+        <v>70.53185562857144</v>
       </c>
       <c r="O10">
-        <v>15.62937240228572</v>
+        <v>15.51700823828572</v>
       </c>
       <c r="P10">
-        <v>55.41322942628572</v>
+        <v>55.01484739028572</v>
       </c>
       <c r="Q10">
-        <v>101.7132294262857</v>
+        <v>101.3148473902857</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1084116405752737</v>
+        <v>0.1089579264109119</v>
       </c>
       <c r="T10">
-        <v>1.445996318135652</v>
+        <v>1.458612619189651</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.38696289580114</v>
+        <v>16.34396701848991</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1026827730339298</v>
+        <v>0.1024881167386078</v>
       </c>
       <c r="C11">
-        <v>851.7860391015172</v>
+        <v>844.7038306699883</v>
       </c>
       <c r="D11">
-        <v>894.5720391015171</v>
+        <v>897.6438306699882</v>
       </c>
       <c r="E11">
-        <v>-300.114</v>
+        <v>-289.96</v>
       </c>
       <c r="F11">
-        <v>91.386</v>
+        <v>101.54</v>
       </c>
       <c r="G11">
         <v>48.6</v>
@@ -2195,28 +2195,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M11">
-        <v>4.596715799999999</v>
+        <v>5.107461999999999</v>
       </c>
       <c r="N11">
-        <v>70.53185562857144</v>
+        <v>70.02110942857144</v>
       </c>
       <c r="O11">
-        <v>15.51700823828572</v>
+        <v>15.40464407428572</v>
       </c>
       <c r="P11">
-        <v>55.01484739028572</v>
+        <v>54.61646535428572</v>
       </c>
       <c r="Q11">
-        <v>101.3148473902857</v>
+        <v>100.9164653542857</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1089579264109119</v>
+        <v>0.1095163519317864</v>
       </c>
       <c r="T11">
-        <v>1.458612619189651</v>
+        <v>1.471509282489294</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.34396701848991</v>
+        <v>14.70957031664092</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1024881167386078</v>
+        <v>0.1022934604432858</v>
       </c>
       <c r="C12">
-        <v>844.7038306699883</v>
+        <v>837.6427908325597</v>
       </c>
       <c r="D12">
-        <v>897.6438306699882</v>
+        <v>900.7367908325597</v>
       </c>
       <c r="E12">
-        <v>-289.96</v>
+        <v>-279.806</v>
       </c>
       <c r="F12">
-        <v>101.54</v>
+        <v>111.694</v>
       </c>
       <c r="G12">
         <v>48.6</v>
@@ -2277,28 +2277,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M12">
-        <v>5.107462</v>
+        <v>5.6182082</v>
       </c>
       <c r="N12">
-        <v>70.02110942857144</v>
+        <v>69.51036322857144</v>
       </c>
       <c r="O12">
-        <v>15.40464407428572</v>
+        <v>15.29227991028572</v>
       </c>
       <c r="P12">
-        <v>54.61646535428572</v>
+        <v>54.21808331828572</v>
       </c>
       <c r="Q12">
-        <v>100.9164653542857</v>
+        <v>100.5180833182857</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1095163519317864</v>
+        <v>0.1100873263407705</v>
       </c>
       <c r="T12">
-        <v>1.471509282489294</v>
+        <v>1.484695758447357</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.70957031664091</v>
+        <v>13.37233665149174</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1022934604432858</v>
+        <v>0.1022392041479638</v>
       </c>
       <c r="C13">
-        <v>837.6427908325597</v>
+        <v>828.3546896712938</v>
       </c>
       <c r="D13">
-        <v>900.7367908325597</v>
+        <v>901.6026896712938</v>
       </c>
       <c r="E13">
-        <v>-279.806</v>
+        <v>-269.652</v>
       </c>
       <c r="F13">
-        <v>111.694</v>
+        <v>121.848</v>
       </c>
       <c r="G13">
         <v>48.6</v>
@@ -2359,45 +2359,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M13">
-        <v>5.6182082</v>
+        <v>6.3117264</v>
       </c>
       <c r="N13">
-        <v>69.51036322857144</v>
+        <v>68.81684502857144</v>
       </c>
       <c r="O13">
-        <v>15.29227991028572</v>
+        <v>15.13970590628572</v>
       </c>
       <c r="P13">
-        <v>54.21808331828572</v>
+        <v>53.67713912228572</v>
       </c>
       <c r="Q13">
-        <v>100.5180833182857</v>
+        <v>99.97713912228572</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1100873263407705</v>
+        <v>0.1106712774408679</v>
       </c>
       <c r="T13">
-        <v>1.484695758447357</v>
+        <v>1.498181927040829</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.37233665149174</v>
+        <v>11.90301459020331</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1022392041479638</v>
+        <v>0.1020562478526417</v>
       </c>
       <c r="C14">
-        <v>828.3546896712938</v>
+        <v>821.1328775482161</v>
       </c>
       <c r="D14">
-        <v>901.6026896712938</v>
+        <v>904.5348775482162</v>
       </c>
       <c r="E14">
-        <v>-269.652</v>
+        <v>-259.498</v>
       </c>
       <c r="F14">
-        <v>121.848</v>
+        <v>132.002</v>
       </c>
       <c r="G14">
         <v>48.6</v>
@@ -2441,28 +2441,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M14">
-        <v>6.3117264</v>
+        <v>6.8377036</v>
       </c>
       <c r="N14">
-        <v>68.81684502857144</v>
+        <v>68.29086782857144</v>
       </c>
       <c r="O14">
-        <v>15.13970590628572</v>
+        <v>15.02399092228572</v>
       </c>
       <c r="P14">
-        <v>53.67713912228572</v>
+        <v>53.26687690628572</v>
       </c>
       <c r="Q14">
-        <v>99.97713912228572</v>
+        <v>99.56687690628571</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1106712774408679</v>
+        <v>0.1112686527041859</v>
       </c>
       <c r="T14">
-        <v>1.498181927040829</v>
+        <v>1.51197812249852</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.90301459020331</v>
+        <v>10.9873980832646</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1020562478526417</v>
+        <v>0.1018732915573197</v>
       </c>
       <c r="C15">
-        <v>821.1328775482161</v>
+        <v>813.930199747959</v>
       </c>
       <c r="D15">
-        <v>904.5348775482162</v>
+        <v>907.4861997479591</v>
       </c>
       <c r="E15">
-        <v>-259.498</v>
+        <v>-249.344</v>
       </c>
       <c r="F15">
-        <v>132.002</v>
+        <v>142.156</v>
       </c>
       <c r="G15">
         <v>48.6</v>
@@ -2523,28 +2523,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M15">
-        <v>6.8377036</v>
+        <v>7.3636808</v>
       </c>
       <c r="N15">
-        <v>68.29086782857144</v>
+        <v>67.76489062857144</v>
       </c>
       <c r="O15">
-        <v>15.02399092228572</v>
+        <v>14.90827593828572</v>
       </c>
       <c r="P15">
-        <v>53.26687690628572</v>
+        <v>52.85661469028572</v>
       </c>
       <c r="Q15">
-        <v>99.56687690628571</v>
+        <v>99.15661469028572</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1112686527041859</v>
+        <v>0.111879920415488</v>
       </c>
       <c r="T15">
-        <v>1.51197812249852</v>
+        <v>1.52609515971104</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.9873980832646</v>
+        <v>10.20258393445998</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1018732915573197</v>
+        <v>0.1018892352619977</v>
       </c>
       <c r="C16">
-        <v>813.930199747959</v>
+        <v>803.5182413019123</v>
       </c>
       <c r="D16">
-        <v>907.4861997479591</v>
+        <v>907.2282413019124</v>
       </c>
       <c r="E16">
-        <v>-249.344</v>
+        <v>-239.19</v>
       </c>
       <c r="F16">
-        <v>142.156</v>
+        <v>152.31</v>
       </c>
       <c r="G16">
         <v>48.6</v>
@@ -2605,45 +2605,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M16">
-        <v>7.3636808</v>
+        <v>8.148585000000001</v>
       </c>
       <c r="N16">
-        <v>67.76489062857144</v>
+        <v>66.97998642857144</v>
       </c>
       <c r="O16">
-        <v>14.90827593828572</v>
+        <v>14.73559701428572</v>
       </c>
       <c r="P16">
-        <v>52.85661469028572</v>
+        <v>52.24438941428572</v>
       </c>
       <c r="Q16">
-        <v>99.15661469028572</v>
+        <v>98.54438941428572</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.111879920415488</v>
+        <v>0.1125055708964679</v>
       </c>
       <c r="T16">
-        <v>1.52609515971104</v>
+        <v>1.540544362505032</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.20258393445998</v>
+        <v>9.219830366692062</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1018892352619977</v>
+        <v>0.1017195389666757</v>
       </c>
       <c r="C17">
-        <v>803.5182413019124</v>
+        <v>796.1173625615888</v>
       </c>
       <c r="D17">
-        <v>907.2282413019124</v>
+        <v>909.9813625615889</v>
       </c>
       <c r="E17">
-        <v>-239.19</v>
+        <v>-229.036</v>
       </c>
       <c r="F17">
-        <v>152.31</v>
+        <v>162.464</v>
       </c>
       <c r="G17">
         <v>48.6</v>
@@ -2687,28 +2687,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M17">
-        <v>8.148585000000001</v>
+        <v>8.691824</v>
       </c>
       <c r="N17">
-        <v>66.97998642857144</v>
+        <v>66.43674742857144</v>
       </c>
       <c r="O17">
-        <v>14.73559701428572</v>
+        <v>14.61608443428572</v>
       </c>
       <c r="P17">
-        <v>52.24438941428572</v>
+        <v>51.82066299428572</v>
       </c>
       <c r="Q17">
-        <v>98.54438941428572</v>
+        <v>98.12066299428571</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1125055708964679</v>
+        <v>0.113146117817471</v>
       </c>
       <c r="T17">
-        <v>1.540544362505032</v>
+        <v>1.555337593936976</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.219830366692062</v>
+        <v>8.643590968773808</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1017195389666757</v>
+        <v>0.1015498426713536</v>
       </c>
       <c r="C18">
-        <v>796.1173625615888</v>
+        <v>788.7332442085935</v>
       </c>
       <c r="D18">
-        <v>909.9813625615889</v>
+        <v>912.7512442085936</v>
       </c>
       <c r="E18">
-        <v>-229.036</v>
+        <v>-218.882</v>
       </c>
       <c r="F18">
-        <v>162.464</v>
+        <v>172.618</v>
       </c>
       <c r="G18">
         <v>48.6</v>
@@ -2769,28 +2769,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M18">
-        <v>8.691824</v>
+        <v>9.235063</v>
       </c>
       <c r="N18">
-        <v>66.43674742857144</v>
+        <v>65.89350842857144</v>
       </c>
       <c r="O18">
-        <v>14.61608443428572</v>
+        <v>14.49657185428572</v>
       </c>
       <c r="P18">
-        <v>51.82066299428572</v>
+        <v>51.39693657428572</v>
       </c>
       <c r="Q18">
-        <v>98.12066299428571</v>
+        <v>97.69693657428571</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.113146117817471</v>
+        <v>0.1138020996040405</v>
       </c>
       <c r="T18">
-        <v>1.555337593936976</v>
+        <v>1.570487288776918</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.643590968773808</v>
+        <v>8.135144441198879</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1015498426713536</v>
+        <v>0.1013801463760316</v>
       </c>
       <c r="C19">
-        <v>788.7332442085935</v>
+        <v>781.3660397604591</v>
       </c>
       <c r="D19">
-        <v>912.7512442085936</v>
+        <v>915.5380397604591</v>
       </c>
       <c r="E19">
-        <v>-218.882</v>
+        <v>-208.728</v>
       </c>
       <c r="F19">
-        <v>172.618</v>
+        <v>182.772</v>
       </c>
       <c r="G19">
         <v>48.6</v>
@@ -2851,28 +2851,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M19">
-        <v>9.235063</v>
+        <v>9.778302</v>
       </c>
       <c r="N19">
-        <v>65.89350842857144</v>
+        <v>65.35026942857144</v>
       </c>
       <c r="O19">
-        <v>14.49657185428572</v>
+        <v>14.37705927428572</v>
       </c>
       <c r="P19">
-        <v>51.39693657428572</v>
+        <v>50.97321015428572</v>
       </c>
       <c r="Q19">
-        <v>97.69693657428571</v>
+        <v>97.27321015428572</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1138020996040405</v>
+        <v>0.11447408094638</v>
       </c>
       <c r="T19">
-        <v>1.570487288776918</v>
+        <v>1.586006488369054</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.135144441198879</v>
+        <v>7.683191972243385</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1013801463760316</v>
+        <v>0.1013290100807096</v>
       </c>
       <c r="C20">
-        <v>781.3660397604594</v>
+        <v>772.0551526398654</v>
       </c>
       <c r="D20">
-        <v>915.5380397604594</v>
+        <v>916.3811526398654</v>
       </c>
       <c r="E20">
-        <v>-208.728</v>
+        <v>-198.574</v>
       </c>
       <c r="F20">
-        <v>182.772</v>
+        <v>192.926</v>
       </c>
       <c r="G20">
         <v>48.6</v>
@@ -2933,45 +2933,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M20">
-        <v>9.778302</v>
+        <v>10.4758818</v>
       </c>
       <c r="N20">
-        <v>65.35026942857144</v>
+        <v>64.65268962857144</v>
       </c>
       <c r="O20">
-        <v>14.37705927428572</v>
+        <v>14.22359171828572</v>
       </c>
       <c r="P20">
-        <v>50.97321015428572</v>
+        <v>50.42909791028572</v>
       </c>
       <c r="Q20">
-        <v>97.27321015428572</v>
+        <v>96.72909791028572</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.11447408094638</v>
+        <v>0.1151626544206291</v>
       </c>
       <c r="T20">
-        <v>1.586006488369054</v>
+        <v>1.601908878074576</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.683191972243385</v>
+        <v>7.171574943559542</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1013290100807096</v>
+        <v>0.1011655537853876</v>
       </c>
       <c r="C21">
-        <v>772.0551526398654</v>
+        <v>764.6065941657291</v>
       </c>
       <c r="D21">
-        <v>916.3811526398654</v>
+        <v>919.0865941657291</v>
       </c>
       <c r="E21">
-        <v>-198.574</v>
+        <v>-188.42</v>
       </c>
       <c r="F21">
-        <v>192.926</v>
+        <v>203.08</v>
       </c>
       <c r="G21">
         <v>48.6</v>
@@ -3015,28 +3015,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M21">
-        <v>10.4758818</v>
+        <v>11.027244</v>
       </c>
       <c r="N21">
-        <v>64.65268962857144</v>
+        <v>64.10132742857144</v>
       </c>
       <c r="O21">
-        <v>14.22359171828572</v>
+        <v>14.10229203428572</v>
       </c>
       <c r="P21">
-        <v>50.42909791028572</v>
+        <v>49.99903539428572</v>
       </c>
       <c r="Q21">
-        <v>96.72909791028572</v>
+        <v>96.29903539428571</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1151626544206291</v>
+        <v>0.1158684422317345</v>
       </c>
       <c r="T21">
-        <v>1.601908878074576</v>
+        <v>1.618208827522736</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.171574943559542</v>
+        <v>6.812996196381564</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1011655537853876</v>
+        <v>0.1010020974900656</v>
       </c>
       <c r="C22">
-        <v>764.6065941657291</v>
+        <v>757.1740575990616</v>
       </c>
       <c r="D22">
-        <v>919.0865941657291</v>
+        <v>921.8080575990616</v>
       </c>
       <c r="E22">
-        <v>-188.42</v>
+        <v>-178.266</v>
       </c>
       <c r="F22">
-        <v>203.08</v>
+        <v>213.234</v>
       </c>
       <c r="G22">
         <v>48.6</v>
@@ -3097,28 +3097,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M22">
-        <v>11.027244</v>
+        <v>11.5786062</v>
       </c>
       <c r="N22">
-        <v>64.10132742857144</v>
+        <v>63.54996522857143</v>
       </c>
       <c r="O22">
-        <v>14.10229203428572</v>
+        <v>13.98099235028572</v>
       </c>
       <c r="P22">
-        <v>49.99903539428572</v>
+        <v>49.56897287828571</v>
       </c>
       <c r="Q22">
-        <v>96.29903539428571</v>
+        <v>95.86897287828572</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1158684422317345</v>
+        <v>0.1165920980886906</v>
       </c>
       <c r="T22">
-        <v>1.618208827522736</v>
+        <v>1.634921433918952</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.812996196381564</v>
+        <v>6.48856780607768</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1010020974900655</v>
+        <v>0.1008386411947435</v>
       </c>
       <c r="C23">
-        <v>757.1740575990621</v>
+        <v>749.7576856876625</v>
       </c>
       <c r="D23">
-        <v>921.8080575990621</v>
+        <v>924.5456856876625</v>
       </c>
       <c r="E23">
-        <v>-178.266</v>
+        <v>-168.112</v>
       </c>
       <c r="F23">
-        <v>213.234</v>
+        <v>223.388</v>
       </c>
       <c r="G23">
         <v>48.6</v>
@@ -3179,28 +3179,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M23">
-        <v>11.5786062</v>
+        <v>12.1299684</v>
       </c>
       <c r="N23">
-        <v>63.54996522857144</v>
+        <v>62.99860302857143</v>
       </c>
       <c r="O23">
-        <v>13.98099235028572</v>
+        <v>13.85969266628572</v>
       </c>
       <c r="P23">
-        <v>49.56897287828572</v>
+        <v>49.13891036228571</v>
       </c>
       <c r="Q23">
-        <v>95.86897287828572</v>
+        <v>95.43891036228571</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1165920980886906</v>
+        <v>0.1173343092240302</v>
       </c>
       <c r="T23">
-        <v>1.634921433918951</v>
+        <v>1.6520625686843</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.488567806077682</v>
+        <v>6.193632905801422</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1008386411947435</v>
+        <v>0.1008545848994215</v>
       </c>
       <c r="C24">
-        <v>749.7576856876625</v>
+        <v>739.3359389886211</v>
       </c>
       <c r="D24">
-        <v>924.5456856876625</v>
+        <v>924.2779389886211</v>
       </c>
       <c r="E24">
-        <v>-168.112</v>
+        <v>-157.958</v>
       </c>
       <c r="F24">
-        <v>223.388</v>
+        <v>233.542</v>
       </c>
       <c r="G24">
         <v>48.6</v>
@@ -3261,45 +3261,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M24">
-        <v>12.1299684</v>
+        <v>12.9148726</v>
       </c>
       <c r="N24">
-        <v>62.99860302857143</v>
+        <v>62.21369882857143</v>
       </c>
       <c r="O24">
-        <v>13.85969266628572</v>
+        <v>13.68701374228571</v>
       </c>
       <c r="P24">
-        <v>49.13891036228571</v>
+        <v>48.52668508628572</v>
       </c>
       <c r="Q24">
-        <v>95.43891036228571</v>
+        <v>94.82668508628572</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1173343092240302</v>
+        <v>0.1180957985706773</v>
       </c>
       <c r="T24">
-        <v>1.6520625686843</v>
+        <v>1.669648927729268</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.193632905801422</v>
+        <v>5.817213514639813</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1008545848994215</v>
+        <v>0.1006989286040995</v>
       </c>
       <c r="C25">
-        <v>739.3359389886211</v>
+        <v>731.8025671773485</v>
       </c>
       <c r="D25">
-        <v>924.2779389886211</v>
+        <v>926.8985671773485</v>
       </c>
       <c r="E25">
-        <v>-157.958</v>
+        <v>-147.804</v>
       </c>
       <c r="F25">
-        <v>233.542</v>
+        <v>243.696</v>
       </c>
       <c r="G25">
         <v>48.6</v>
@@ -3343,28 +3343,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M25">
-        <v>12.9148726</v>
+        <v>13.4763888</v>
       </c>
       <c r="N25">
-        <v>62.21369882857143</v>
+        <v>61.65218262857143</v>
       </c>
       <c r="O25">
-        <v>13.68701374228571</v>
+        <v>13.56348017828572</v>
       </c>
       <c r="P25">
-        <v>48.52668508628572</v>
+        <v>48.08870245028572</v>
       </c>
       <c r="Q25">
-        <v>94.82668508628572</v>
+        <v>94.38870245028571</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1180957985706773</v>
+        <v>0.1188773271106572</v>
       </c>
       <c r="T25">
-        <v>1.669648927729268</v>
+        <v>1.687698085696472</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.817213514639813</v>
+        <v>5.574829618196487</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1006989286040995</v>
+        <v>0.1005432723087775</v>
       </c>
       <c r="C26">
-        <v>731.8025671773485</v>
+        <v>724.2840982850312</v>
       </c>
       <c r="D26">
-        <v>926.8985671773485</v>
+        <v>929.5340982850312</v>
       </c>
       <c r="E26">
-        <v>-147.804</v>
+        <v>-137.65</v>
       </c>
       <c r="F26">
-        <v>243.696</v>
+        <v>253.85</v>
       </c>
       <c r="G26">
         <v>48.6</v>
@@ -3425,28 +3425,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M26">
-        <v>13.4763888</v>
+        <v>14.037905</v>
       </c>
       <c r="N26">
-        <v>61.65218262857143</v>
+        <v>61.09066642857143</v>
       </c>
       <c r="O26">
-        <v>13.56348017828572</v>
+        <v>13.43994661428571</v>
       </c>
       <c r="P26">
-        <v>48.08870245028572</v>
+        <v>47.65071981428571</v>
       </c>
       <c r="Q26">
-        <v>94.38870245028571</v>
+        <v>93.95071981428572</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1188773271106572</v>
+        <v>0.1196796964117033</v>
       </c>
       <c r="T26">
-        <v>1.687698085696472</v>
+        <v>1.706228554542802</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.574829618196488</v>
+        <v>5.351836433468629</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1005432723087775</v>
+        <v>0.1003876160134555</v>
       </c>
       <c r="C27">
-        <v>724.2840982850312</v>
+        <v>716.7806597984496</v>
       </c>
       <c r="D27">
-        <v>929.5340982850312</v>
+        <v>932.1846597984496</v>
       </c>
       <c r="E27">
-        <v>-137.65</v>
+        <v>-127.496</v>
       </c>
       <c r="F27">
-        <v>253.85</v>
+        <v>264.004</v>
       </c>
       <c r="G27">
         <v>48.6</v>
@@ -3507,28 +3507,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M27">
-        <v>14.037905</v>
+        <v>14.5994212</v>
       </c>
       <c r="N27">
-        <v>61.09066642857143</v>
+        <v>60.52915022857143</v>
       </c>
       <c r="O27">
-        <v>13.43994661428571</v>
+        <v>13.31641305028572</v>
       </c>
       <c r="P27">
-        <v>47.65071981428571</v>
+        <v>47.21273717828571</v>
       </c>
       <c r="Q27">
-        <v>93.95071981428572</v>
+        <v>93.5127371782857</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1196796964117033</v>
+        <v>0.1205037513695344</v>
       </c>
       <c r="T27">
-        <v>1.706228554542802</v>
+        <v>1.725259846871464</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.351836433468629</v>
+        <v>5.145996570642912</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1003876160134555</v>
+        <v>0.1002319597181334</v>
       </c>
       <c r="C28">
-        <v>716.7806597984496</v>
+        <v>709.2923806626558</v>
       </c>
       <c r="D28">
-        <v>932.1846597984496</v>
+        <v>934.8503806626558</v>
       </c>
       <c r="E28">
-        <v>-127.496</v>
+        <v>-117.342</v>
       </c>
       <c r="F28">
-        <v>264.004</v>
+        <v>274.158</v>
       </c>
       <c r="G28">
         <v>48.6</v>
@@ -3589,28 +3589,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M28">
-        <v>14.5994212</v>
+        <v>15.1609374</v>
       </c>
       <c r="N28">
-        <v>60.52915022857143</v>
+        <v>59.96763402857143</v>
       </c>
       <c r="O28">
-        <v>13.31641305028572</v>
+        <v>13.19287948628572</v>
       </c>
       <c r="P28">
-        <v>47.21273717828571</v>
+        <v>46.77475454228572</v>
       </c>
       <c r="Q28">
-        <v>93.5127371782857</v>
+        <v>93.07475454228572</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1205037513695344</v>
+        <v>0.1213503831755252</v>
       </c>
       <c r="T28">
-        <v>1.725259846871464</v>
+        <v>1.744812544469405</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.145996570642912</v>
+        <v>4.955404105063545</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1002319597181334</v>
+        <v>0.1000763034228114</v>
       </c>
       <c r="C29">
-        <v>709.2923806626558</v>
+        <v>701.8193913018799</v>
       </c>
       <c r="D29">
-        <v>934.8503806626558</v>
+        <v>937.5313913018799</v>
       </c>
       <c r="E29">
-        <v>-117.342</v>
+        <v>-107.188</v>
       </c>
       <c r="F29">
-        <v>274.158</v>
+        <v>284.312</v>
       </c>
       <c r="G29">
         <v>48.6</v>
@@ -3671,28 +3671,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M29">
-        <v>15.1609374</v>
+        <v>15.7224536</v>
       </c>
       <c r="N29">
-        <v>59.96763402857143</v>
+        <v>59.40611782857143</v>
       </c>
       <c r="O29">
-        <v>13.19287948628572</v>
+        <v>13.06934592228571</v>
       </c>
       <c r="P29">
-        <v>46.77475454228572</v>
+        <v>46.33677190628572</v>
       </c>
       <c r="Q29">
-        <v>93.07475454228572</v>
+        <v>92.63677190628572</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1213503831755252</v>
+        <v>0.1222205325316825</v>
       </c>
       <c r="T29">
-        <v>1.744812544469405</v>
+        <v>1.764908372556178</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.955404105063545</v>
+        <v>4.778425387025561</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1000763034228114</v>
+        <v>0.09992064712748938</v>
       </c>
       <c r="C30">
-        <v>701.8193913018799</v>
+        <v>694.3618236408059</v>
       </c>
       <c r="D30">
-        <v>937.5313913018799</v>
+        <v>940.2278236408059</v>
       </c>
       <c r="E30">
-        <v>-107.188</v>
+        <v>-97.03399999999999</v>
       </c>
       <c r="F30">
-        <v>284.312</v>
+        <v>294.466</v>
       </c>
       <c r="G30">
         <v>48.6</v>
@@ -3753,28 +3753,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M30">
-        <v>15.7224536</v>
+        <v>16.2839698</v>
       </c>
       <c r="N30">
-        <v>59.40611782857143</v>
+        <v>58.84460162857143</v>
       </c>
       <c r="O30">
-        <v>13.06934592228571</v>
+        <v>12.94581235828572</v>
       </c>
       <c r="P30">
-        <v>46.33677190628572</v>
+        <v>45.89878927028572</v>
       </c>
       <c r="Q30">
-        <v>92.63677190628572</v>
+        <v>92.19878927028572</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1222205325316825</v>
+        <v>0.123115193137309</v>
       </c>
       <c r="T30">
-        <v>1.764908372556178</v>
+        <v>1.785570280307367</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.778425387025561</v>
+        <v>4.613652097817783</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09992064712748937</v>
+        <v>0.1003499908321673</v>
       </c>
       <c r="C31">
-        <v>694.3618236408063</v>
+        <v>676.8076226346273</v>
       </c>
       <c r="D31">
-        <v>940.2278236408062</v>
+        <v>932.8276226346272</v>
       </c>
       <c r="E31">
-        <v>-97.03400000000005</v>
+        <v>-86.88</v>
       </c>
       <c r="F31">
-        <v>294.466</v>
+        <v>304.62</v>
       </c>
       <c r="G31">
         <v>48.6</v>
@@ -3835,45 +3835,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M31">
-        <v>16.2839698</v>
+        <v>17.607036</v>
       </c>
       <c r="N31">
-        <v>58.84460162857144</v>
+        <v>57.52153542857143</v>
       </c>
       <c r="O31">
-        <v>12.94581235828572</v>
+        <v>12.65473779428572</v>
       </c>
       <c r="P31">
-        <v>45.89878927028573</v>
+        <v>44.86679763428572</v>
       </c>
       <c r="Q31">
-        <v>92.19878927028572</v>
+        <v>91.16679763428571</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.123115193137309</v>
+        <v>0.1240354154745248</v>
       </c>
       <c r="T31">
-        <v>1.785570280307367</v>
+        <v>1.806822528280019</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.613652097817784</v>
+        <v>4.266963015726862</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1003499908321673</v>
+        <v>0.1002138345368453</v>
       </c>
       <c r="C32">
-        <v>676.8076226346273</v>
+        <v>668.9877781734353</v>
       </c>
       <c r="D32">
-        <v>932.8276226346272</v>
+        <v>935.1617781734353</v>
       </c>
       <c r="E32">
-        <v>-86.88</v>
+        <v>-76.726</v>
       </c>
       <c r="F32">
-        <v>304.62</v>
+        <v>314.774</v>
       </c>
       <c r="G32">
         <v>48.6</v>
@@ -3917,28 +3917,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M32">
-        <v>17.607036</v>
+        <v>18.1939372</v>
       </c>
       <c r="N32">
-        <v>57.52153542857143</v>
+        <v>56.93463422857143</v>
       </c>
       <c r="O32">
-        <v>12.65473779428572</v>
+        <v>12.52561953028571</v>
       </c>
       <c r="P32">
-        <v>44.86679763428572</v>
+        <v>44.40901469828572</v>
       </c>
       <c r="Q32">
-        <v>91.16679763428571</v>
+        <v>90.70901469828571</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1240354154745248</v>
+        <v>0.1249823109229643</v>
       </c>
       <c r="T32">
-        <v>1.806822528280019</v>
+        <v>1.828690783440284</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.266963015726862</v>
+        <v>4.129319047477608</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1002138345368453</v>
+        <v>0.1000776782415233</v>
       </c>
       <c r="C33">
-        <v>668.9877781734353</v>
+        <v>661.1796442341805</v>
       </c>
       <c r="D33">
-        <v>935.1617781734353</v>
+        <v>937.5076442341805</v>
       </c>
       <c r="E33">
-        <v>-76.726</v>
+        <v>-66.572</v>
       </c>
       <c r="F33">
-        <v>314.774</v>
+        <v>324.928</v>
       </c>
       <c r="G33">
         <v>48.6</v>
@@ -3999,28 +3999,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M33">
-        <v>18.1939372</v>
+        <v>18.7808384</v>
       </c>
       <c r="N33">
-        <v>56.93463422857143</v>
+        <v>56.34773302857143</v>
       </c>
       <c r="O33">
-        <v>12.52561953028571</v>
+        <v>12.39650126628572</v>
       </c>
       <c r="P33">
-        <v>44.40901469828572</v>
+        <v>43.95123176228572</v>
       </c>
       <c r="Q33">
-        <v>90.70901469828571</v>
+        <v>90.25123176228571</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1249823109229643</v>
+        <v>0.1259570562375343</v>
       </c>
       <c r="T33">
-        <v>1.828690783440284</v>
+        <v>1.85120222257585</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.129319047477608</v>
+        <v>4.000277827243933</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1000776782415233</v>
+        <v>0.1008424219462013</v>
       </c>
       <c r="C34">
-        <v>661.1796442341805</v>
+        <v>638.0001805342672</v>
       </c>
       <c r="D34">
-        <v>937.5076442341805</v>
+        <v>924.4821805342672</v>
       </c>
       <c r="E34">
-        <v>-66.572</v>
+        <v>-56.41800000000001</v>
       </c>
       <c r="F34">
-        <v>324.928</v>
+        <v>335.082</v>
       </c>
       <c r="G34">
         <v>48.6</v>
@@ -4081,45 +4081,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M34">
-        <v>18.7808384</v>
+        <v>20.5405266</v>
       </c>
       <c r="N34">
-        <v>56.34773302857143</v>
+        <v>54.58804482857143</v>
       </c>
       <c r="O34">
-        <v>12.39650126628572</v>
+        <v>12.00936986228572</v>
       </c>
       <c r="P34">
-        <v>43.95123176228572</v>
+        <v>42.57867496628572</v>
       </c>
       <c r="Q34">
-        <v>90.25123176228571</v>
+        <v>88.87867496628571</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1259570562375343</v>
+        <v>0.1269608984271661</v>
       </c>
       <c r="T34">
-        <v>1.85120222257585</v>
+        <v>1.874385644969195</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.000277827243933</v>
+        <v>3.657577670310139</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1008424219462013</v>
+        <v>0.1007335656508793</v>
       </c>
       <c r="C35">
-        <v>638.0001805342672</v>
+        <v>629.6781334408703</v>
       </c>
       <c r="D35">
-        <v>924.4821805342672</v>
+        <v>926.3141334408703</v>
       </c>
       <c r="E35">
-        <v>-56.41800000000001</v>
+        <v>-46.26400000000001</v>
       </c>
       <c r="F35">
-        <v>335.082</v>
+        <v>345.236</v>
       </c>
       <c r="G35">
         <v>48.6</v>
@@ -4163,28 +4163,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M35">
-        <v>20.5405266</v>
+        <v>21.1629668</v>
       </c>
       <c r="N35">
-        <v>54.58804482857143</v>
+        <v>53.96560462857143</v>
       </c>
       <c r="O35">
-        <v>12.00936986228572</v>
+        <v>11.87243301828572</v>
       </c>
       <c r="P35">
-        <v>42.57867496628572</v>
+        <v>42.09317161028572</v>
       </c>
       <c r="Q35">
-        <v>88.87867496628571</v>
+        <v>88.39317161028572</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1269608984271661</v>
+        <v>0.1279951600770898</v>
       </c>
       <c r="T35">
-        <v>1.874385644969195</v>
+        <v>1.898271595313853</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.657577670310139</v>
+        <v>3.550001856477488</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1007335656508793</v>
+        <v>0.1013891093555573</v>
       </c>
       <c r="C36">
-        <v>629.6781334408703</v>
+        <v>608.6004218403225</v>
       </c>
       <c r="D36">
-        <v>926.3141334408703</v>
+        <v>915.3904218403226</v>
       </c>
       <c r="E36">
-        <v>-46.26400000000001</v>
+        <v>-36.10999999999996</v>
       </c>
       <c r="F36">
-        <v>345.236</v>
+        <v>355.39</v>
       </c>
       <c r="G36">
         <v>48.6</v>
@@ -4245,45 +4245,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M36">
-        <v>21.1629668</v>
+        <v>22.780499</v>
       </c>
       <c r="N36">
-        <v>53.96560462857143</v>
+        <v>52.34807242857143</v>
       </c>
       <c r="O36">
-        <v>11.87243301828572</v>
+        <v>11.51657593428571</v>
       </c>
       <c r="P36">
-        <v>42.09317161028572</v>
+        <v>40.83149649428572</v>
       </c>
       <c r="Q36">
-        <v>88.39317161028572</v>
+        <v>87.13149649428571</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1279951600770898</v>
+        <v>0.1290612451623958</v>
       </c>
       <c r="T36">
-        <v>1.898271595313853</v>
+        <v>1.922892497976808</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.550001856477488</v>
+        <v>3.297933527644474</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1013891093555573</v>
+        <v>0.1013020930602352</v>
       </c>
       <c r="C37">
-        <v>608.6004218403225</v>
+        <v>599.8815728209418</v>
       </c>
       <c r="D37">
-        <v>915.3904218403226</v>
+        <v>916.8255728209417</v>
       </c>
       <c r="E37">
-        <v>-36.10999999999996</v>
+        <v>-25.95599999999996</v>
       </c>
       <c r="F37">
-        <v>355.39</v>
+        <v>365.544</v>
       </c>
       <c r="G37">
         <v>48.6</v>
@@ -4327,28 +4327,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M37">
-        <v>22.780499</v>
+        <v>23.43137040000001</v>
       </c>
       <c r="N37">
-        <v>52.34807242857143</v>
+        <v>51.69720102857143</v>
       </c>
       <c r="O37">
-        <v>11.51657593428571</v>
+        <v>11.37338422628571</v>
       </c>
       <c r="P37">
-        <v>40.83149649428572</v>
+        <v>40.32381680228571</v>
       </c>
       <c r="Q37">
-        <v>87.13149649428571</v>
+        <v>86.62381680228572</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1290612451623958</v>
+        <v>0.1301606454066176</v>
       </c>
       <c r="T37">
-        <v>1.922892497976808</v>
+        <v>1.948282803847981</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.297933527644474</v>
+        <v>3.206324262987683</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1013020930602352</v>
+        <v>0.1012150767649132</v>
       </c>
       <c r="C38">
-        <v>599.8815728209418</v>
+        <v>591.1672309331523</v>
       </c>
       <c r="D38">
-        <v>916.8255728209417</v>
+        <v>918.2652309331522</v>
       </c>
       <c r="E38">
-        <v>-25.95600000000002</v>
+        <v>-15.80200000000002</v>
       </c>
       <c r="F38">
-        <v>365.544</v>
+        <v>375.698</v>
       </c>
       <c r="G38">
         <v>48.6</v>
@@ -4409,28 +4409,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M38">
-        <v>23.4313704</v>
+        <v>24.0822418</v>
       </c>
       <c r="N38">
-        <v>51.69720102857143</v>
+        <v>51.04632962857143</v>
       </c>
       <c r="O38">
-        <v>11.37338422628572</v>
+        <v>11.23019251828572</v>
       </c>
       <c r="P38">
-        <v>40.32381680228572</v>
+        <v>39.81613711028572</v>
       </c>
       <c r="Q38">
-        <v>86.62381680228572</v>
+        <v>86.11613711028572</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1301606454066175</v>
+        <v>0.131294947245894</v>
       </c>
       <c r="T38">
-        <v>1.948282803847981</v>
+        <v>1.974479151175381</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.206324262987684</v>
+        <v>3.119666850474503</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1012150767649132</v>
+        <v>0.1011280604695912</v>
       </c>
       <c r="C39">
-        <v>591.1672309331523</v>
+        <v>582.4574174425048</v>
       </c>
       <c r="D39">
-        <v>918.2652309331522</v>
+        <v>919.7094174425048</v>
       </c>
       <c r="E39">
-        <v>-15.80200000000002</v>
+        <v>-5.648000000000025</v>
       </c>
       <c r="F39">
-        <v>375.698</v>
+        <v>385.852</v>
       </c>
       <c r="G39">
         <v>48.6</v>
@@ -4491,28 +4491,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M39">
-        <v>24.0822418</v>
+        <v>24.7331132</v>
       </c>
       <c r="N39">
-        <v>51.04632962857143</v>
+        <v>50.39545822857143</v>
       </c>
       <c r="O39">
-        <v>11.23019251828572</v>
+        <v>11.08700081028571</v>
       </c>
       <c r="P39">
-        <v>39.81613711028572</v>
+        <v>39.30845741828571</v>
       </c>
       <c r="Q39">
-        <v>86.11613711028572</v>
+        <v>85.60845741828571</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.131294947245894</v>
+        <v>0.1324658394670825</v>
       </c>
       <c r="T39">
-        <v>1.974479151175381</v>
+        <v>2.001520541964955</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.119666850474503</v>
+        <v>3.037570354409385</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1011280604695912</v>
+        <v>0.1034138041742692</v>
       </c>
       <c r="C40">
-        <v>582.4574174425048</v>
+        <v>535.8152868428742</v>
       </c>
       <c r="D40">
-        <v>919.7094174425048</v>
+        <v>883.2212868428743</v>
       </c>
       <c r="E40">
-        <v>-5.648000000000025</v>
+        <v>4.506000000000029</v>
       </c>
       <c r="F40">
-        <v>385.852</v>
+        <v>396.006</v>
       </c>
       <c r="G40">
         <v>48.6</v>
@@ -4573,45 +4573,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M40">
-        <v>24.7331132</v>
+        <v>28.4728314</v>
       </c>
       <c r="N40">
-        <v>50.39545822857143</v>
+        <v>46.65574002857143</v>
       </c>
       <c r="O40">
-        <v>11.08700081028571</v>
+        <v>10.26426280628571</v>
       </c>
       <c r="P40">
-        <v>39.30845741828571</v>
+        <v>36.39147722228572</v>
       </c>
       <c r="Q40">
-        <v>85.60845741828571</v>
+        <v>82.69147722228571</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1324658394670825</v>
+        <v>0.1336751215971626</v>
       </c>
       <c r="T40">
-        <v>2.001520541964955</v>
+        <v>2.029448535731238</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.037570354409385</v>
+        <v>2.638605566588345</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1034138041742692</v>
+        <v>0.1033876278789471</v>
       </c>
       <c r="C41">
-        <v>535.8152868428742</v>
+        <v>526.0627526106205</v>
       </c>
       <c r="D41">
-        <v>883.2212868428743</v>
+        <v>883.6227526106204</v>
       </c>
       <c r="E41">
-        <v>4.506000000000029</v>
+        <v>14.66000000000003</v>
       </c>
       <c r="F41">
-        <v>396.006</v>
+        <v>406.16</v>
       </c>
       <c r="G41">
         <v>48.6</v>
@@ -4655,28 +4655,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M41">
-        <v>28.4728314</v>
+        <v>29.202904</v>
       </c>
       <c r="N41">
-        <v>46.65574002857143</v>
+        <v>45.92566742857143</v>
       </c>
       <c r="O41">
-        <v>10.26426280628571</v>
+        <v>10.10364683428571</v>
       </c>
       <c r="P41">
-        <v>36.39147722228572</v>
+        <v>35.82202059428572</v>
       </c>
       <c r="Q41">
-        <v>82.69147722228571</v>
+        <v>82.12202059428571</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1336751215971626</v>
+        <v>0.1349247131315786</v>
       </c>
       <c r="T41">
-        <v>2.029448535731238</v>
+        <v>2.058307462623062</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.638605566588345</v>
+        <v>2.572640427423637</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1033876278789471</v>
+        <v>0.1033614515836251</v>
       </c>
       <c r="C42">
-        <v>526.0627526106205</v>
+        <v>516.3105835146237</v>
       </c>
       <c r="D42">
-        <v>883.6227526106204</v>
+        <v>884.0245835146236</v>
       </c>
       <c r="E42">
-        <v>14.66000000000003</v>
+        <v>24.81400000000002</v>
       </c>
       <c r="F42">
-        <v>406.16</v>
+        <v>416.314</v>
       </c>
       <c r="G42">
         <v>48.6</v>
@@ -4737,28 +4737,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M42">
-        <v>29.202904</v>
+        <v>29.9329766</v>
       </c>
       <c r="N42">
-        <v>45.92566742857143</v>
+        <v>45.19559482857143</v>
       </c>
       <c r="O42">
-        <v>10.10364683428571</v>
+        <v>9.943030862285715</v>
       </c>
       <c r="P42">
-        <v>35.82202059428572</v>
+        <v>35.25256396628571</v>
       </c>
       <c r="Q42">
-        <v>82.12202059428571</v>
+        <v>81.5525639662857</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1349247131315786</v>
+        <v>0.1362166637010595</v>
       </c>
       <c r="T42">
-        <v>2.058307462623062</v>
+        <v>2.088144658223084</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.572640427423637</v>
+        <v>2.509893099925499</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1033614515836251</v>
+        <v>0.1046129152883031</v>
       </c>
       <c r="C43">
-        <v>516.3105835146237</v>
+        <v>487.3456697061792</v>
       </c>
       <c r="D43">
-        <v>884.0245835146236</v>
+        <v>865.2136697061792</v>
       </c>
       <c r="E43">
-        <v>24.81400000000002</v>
+        <v>34.96800000000002</v>
       </c>
       <c r="F43">
-        <v>416.314</v>
+        <v>426.468</v>
       </c>
       <c r="G43">
         <v>48.6</v>
@@ -4819,45 +4819,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M43">
-        <v>29.9329766</v>
+        <v>32.3262744</v>
       </c>
       <c r="N43">
-        <v>45.19559482857143</v>
+        <v>42.80229702857143</v>
       </c>
       <c r="O43">
-        <v>9.943030862285715</v>
+        <v>9.416505346285716</v>
       </c>
       <c r="P43">
-        <v>35.25256396628571</v>
+        <v>33.38579168228571</v>
       </c>
       <c r="Q43">
-        <v>81.5525639662857</v>
+        <v>79.68579168228571</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1362166637010595</v>
+        <v>0.1375531642901778</v>
       </c>
       <c r="T43">
-        <v>2.088144658223084</v>
+        <v>2.1190107226369</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.509893099925499</v>
+        <v>2.324071450329934</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1046129152883031</v>
+        <v>0.1046171589929811</v>
       </c>
       <c r="C44">
-        <v>487.3456697061788</v>
+        <v>477.1292438535804</v>
       </c>
       <c r="D44">
-        <v>865.2136697061787</v>
+        <v>865.1512438535804</v>
       </c>
       <c r="E44">
-        <v>34.96799999999996</v>
+        <v>45.12199999999996</v>
       </c>
       <c r="F44">
-        <v>426.468</v>
+        <v>436.622</v>
       </c>
       <c r="G44">
         <v>48.6</v>
@@ -4901,28 +4901,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M44">
-        <v>32.3262744</v>
+        <v>33.0959476</v>
       </c>
       <c r="N44">
-        <v>42.80229702857143</v>
+        <v>42.03262382857143</v>
       </c>
       <c r="O44">
-        <v>9.416505346285716</v>
+        <v>9.247177242285716</v>
       </c>
       <c r="P44">
-        <v>33.38579168228571</v>
+        <v>32.78544658628572</v>
       </c>
       <c r="Q44">
-        <v>79.68579168228571</v>
+        <v>79.08544658628571</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1375531642901778</v>
+        <v>0.1389365596368089</v>
       </c>
       <c r="T44">
-        <v>2.1190107226369</v>
+        <v>2.15095980685471</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.324071450329934</v>
+        <v>2.270023277066447</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1046171589929811</v>
+        <v>0.1046214026976591</v>
       </c>
       <c r="C45">
-        <v>477.1292438535804</v>
+        <v>466.9128270084809</v>
       </c>
       <c r="D45">
-        <v>865.1512438535804</v>
+        <v>865.0888270084808</v>
       </c>
       <c r="E45">
-        <v>45.12199999999996</v>
+        <v>55.27600000000001</v>
       </c>
       <c r="F45">
-        <v>436.622</v>
+        <v>446.776</v>
       </c>
       <c r="G45">
         <v>48.6</v>
@@ -4983,28 +4983,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M45">
-        <v>33.0959476</v>
+        <v>33.8656208</v>
       </c>
       <c r="N45">
-        <v>42.03262382857143</v>
+        <v>41.26295062857143</v>
       </c>
       <c r="O45">
-        <v>9.247177242285716</v>
+        <v>9.077849138285716</v>
       </c>
       <c r="P45">
-        <v>32.78544658628572</v>
+        <v>32.18510149028572</v>
       </c>
       <c r="Q45">
-        <v>79.08544658628571</v>
+        <v>78.48510149028571</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1389365596368089</v>
+        <v>0.1403693619601055</v>
       </c>
       <c r="T45">
-        <v>2.15095980685471</v>
+        <v>2.184049929794584</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.270023277066447</v>
+        <v>2.218431838951301</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1046214026976591</v>
+        <v>0.104625646402337</v>
       </c>
       <c r="C46">
-        <v>466.9128270084809</v>
+        <v>456.696419168932</v>
       </c>
       <c r="D46">
-        <v>865.0888270084808</v>
+        <v>865.026419168932</v>
       </c>
       <c r="E46">
-        <v>55.27600000000001</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="F46">
-        <v>446.776</v>
+        <v>456.93</v>
       </c>
       <c r="G46">
         <v>48.6</v>
@@ -5065,28 +5065,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M46">
-        <v>33.8656208</v>
+        <v>34.635294</v>
       </c>
       <c r="N46">
-        <v>41.26295062857143</v>
+        <v>40.49327742857143</v>
       </c>
       <c r="O46">
-        <v>9.077849138285716</v>
+        <v>8.908521034285714</v>
       </c>
       <c r="P46">
-        <v>32.18510149028572</v>
+        <v>31.58475639428572</v>
       </c>
       <c r="Q46">
-        <v>78.48510149028571</v>
+        <v>77.88475639428572</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1403693619601055</v>
+        <v>0.1418542661860673</v>
       </c>
       <c r="T46">
-        <v>2.184049929794584</v>
+        <v>2.218343329932272</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.218431838951301</v>
+        <v>2.169133353641272</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.104625646402337</v>
+        <v>0.104629890107015</v>
       </c>
       <c r="C47">
-        <v>456.696419168932</v>
+        <v>446.4800203329845</v>
       </c>
       <c r="D47">
-        <v>865.026419168932</v>
+        <v>864.9640203329844</v>
       </c>
       <c r="E47">
-        <v>65.43000000000001</v>
+        <v>75.584</v>
       </c>
       <c r="F47">
-        <v>456.93</v>
+        <v>467.084</v>
       </c>
       <c r="G47">
         <v>48.6</v>
@@ -5147,28 +5147,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M47">
-        <v>34.635294</v>
+        <v>35.4049672</v>
       </c>
       <c r="N47">
-        <v>40.49327742857143</v>
+        <v>39.72360422857143</v>
       </c>
       <c r="O47">
-        <v>8.908521034285714</v>
+        <v>8.739192930285714</v>
       </c>
       <c r="P47">
-        <v>31.58475639428572</v>
+        <v>30.98441129828572</v>
       </c>
       <c r="Q47">
-        <v>77.88475639428572</v>
+        <v>77.28441129828572</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1418542661860673</v>
+        <v>0.1433941668648426</v>
       </c>
       <c r="T47">
-        <v>2.218343329932272</v>
+        <v>2.253906856000985</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.169133353641272</v>
+        <v>2.121978280736027</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.104629890107015</v>
+        <v>0.104634133811693</v>
       </c>
       <c r="C48">
-        <v>446.4800203329845</v>
+        <v>436.2636304986898</v>
       </c>
       <c r="D48">
-        <v>864.9640203329844</v>
+        <v>864.9016304986898</v>
       </c>
       <c r="E48">
-        <v>75.584</v>
+        <v>85.738</v>
       </c>
       <c r="F48">
-        <v>467.084</v>
+        <v>477.238</v>
       </c>
       <c r="G48">
         <v>48.6</v>
@@ -5229,28 +5229,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M48">
-        <v>35.4049672</v>
+        <v>36.1746404</v>
       </c>
       <c r="N48">
-        <v>39.72360422857143</v>
+        <v>38.95393102857143</v>
       </c>
       <c r="O48">
-        <v>8.739192930285714</v>
+        <v>8.569864826285714</v>
       </c>
       <c r="P48">
-        <v>30.98441129828572</v>
+        <v>30.38406620228572</v>
       </c>
       <c r="Q48">
-        <v>77.28441129828572</v>
+        <v>76.68406620228572</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1433941668648426</v>
+        <v>0.1449921770031943</v>
       </c>
       <c r="T48">
-        <v>2.253906856000985</v>
+        <v>2.290812401921348</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.121978280736027</v>
+        <v>2.076829806677813</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.104634133811693</v>
+        <v>0.104638377516371</v>
       </c>
       <c r="C49">
-        <v>436.2636304986898</v>
+        <v>426.0472496641008</v>
       </c>
       <c r="D49">
-        <v>864.9016304986898</v>
+        <v>864.8392496641009</v>
       </c>
       <c r="E49">
-        <v>85.738</v>
+        <v>95.89200000000005</v>
       </c>
       <c r="F49">
-        <v>477.238</v>
+        <v>487.3920000000001</v>
       </c>
       <c r="G49">
         <v>48.6</v>
@@ -5311,28 +5311,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M49">
-        <v>36.1746404</v>
+        <v>36.94431360000001</v>
       </c>
       <c r="N49">
-        <v>38.95393102857143</v>
+        <v>38.18425782857143</v>
       </c>
       <c r="O49">
-        <v>8.569864826285714</v>
+        <v>8.400536722285713</v>
       </c>
       <c r="P49">
-        <v>30.38406620228572</v>
+        <v>29.78372110628571</v>
       </c>
       <c r="Q49">
-        <v>76.68406620228572</v>
+        <v>76.08372110628571</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1449921770031943</v>
+        <v>0.1466516490699442</v>
       </c>
       <c r="T49">
-        <v>2.290812401921348</v>
+        <v>2.32913739191557</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.076829806677813</v>
+        <v>2.033562519038692</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.104638377516371</v>
+        <v>0.1100698612210489</v>
       </c>
       <c r="C50">
-        <v>426.0472496641009</v>
+        <v>342.8051769271698</v>
       </c>
       <c r="D50">
-        <v>864.8392496641009</v>
+        <v>791.7511769271698</v>
       </c>
       <c r="E50">
-        <v>95.892</v>
+        <v>106.046</v>
       </c>
       <c r="F50">
-        <v>487.392</v>
+        <v>497.546</v>
       </c>
       <c r="G50">
         <v>48.6</v>
@@ -5393,45 +5393,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M50">
-        <v>36.9443136</v>
+        <v>44.77914</v>
       </c>
       <c r="N50">
-        <v>38.18425782857143</v>
+        <v>30.34943142857144</v>
       </c>
       <c r="O50">
-        <v>8.400536722285715</v>
+        <v>6.676874914285716</v>
       </c>
       <c r="P50">
-        <v>29.78372110628572</v>
+        <v>23.67255651428572</v>
       </c>
       <c r="Q50">
-        <v>76.08372110628571</v>
+        <v>69.97255651428571</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1466516490699442</v>
+        <v>0.148376198472645</v>
       </c>
       <c r="T50">
-        <v>2.32913739191557</v>
+        <v>2.36896532269388</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.033562519038693</v>
+        <v>1.677758247000086</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1100698612210489</v>
+        <v>0.1101848649257269</v>
       </c>
       <c r="C51">
-        <v>342.8051769271698</v>
+        <v>331.2369576283515</v>
       </c>
       <c r="D51">
-        <v>791.7511769271698</v>
+        <v>790.3369576283515</v>
       </c>
       <c r="E51">
-        <v>106.046</v>
+        <v>116.2</v>
       </c>
       <c r="F51">
-        <v>497.546</v>
+        <v>507.7</v>
       </c>
       <c r="G51">
         <v>48.6</v>
@@ -5475,28 +5475,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M51">
-        <v>44.77914</v>
+        <v>45.693</v>
       </c>
       <c r="N51">
-        <v>30.34943142857144</v>
+        <v>29.43557142857144</v>
       </c>
       <c r="O51">
-        <v>6.676874914285716</v>
+        <v>6.475825714285716</v>
       </c>
       <c r="P51">
-        <v>23.67255651428572</v>
+        <v>22.95974571428572</v>
       </c>
       <c r="Q51">
-        <v>69.97255651428571</v>
+        <v>69.25974571428571</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.148376198472645</v>
+        <v>0.1501697298514539</v>
       </c>
       <c r="T51">
-        <v>2.36896532269388</v>
+        <v>2.410386370703323</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.677758247000086</v>
+        <v>1.644203082060084</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1101848649257269</v>
+        <v>0.1102998686304049</v>
       </c>
       <c r="C52">
-        <v>331.2369576283515</v>
+        <v>319.6737814547996</v>
       </c>
       <c r="D52">
-        <v>790.3369576283515</v>
+        <v>788.9277814547996</v>
       </c>
       <c r="E52">
-        <v>116.2</v>
+        <v>126.354</v>
       </c>
       <c r="F52">
-        <v>507.7</v>
+        <v>517.854</v>
       </c>
       <c r="G52">
         <v>48.6</v>
@@ -5557,28 +5557,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M52">
-        <v>45.693</v>
+        <v>46.60686</v>
       </c>
       <c r="N52">
-        <v>29.43557142857144</v>
+        <v>28.52171142857143</v>
       </c>
       <c r="O52">
-        <v>6.475825714285716</v>
+        <v>6.274776514285715</v>
       </c>
       <c r="P52">
-        <v>22.95974571428572</v>
+        <v>22.24693491428571</v>
       </c>
       <c r="Q52">
-        <v>69.25974571428571</v>
+        <v>68.54693491428571</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1501697298514539</v>
+        <v>0.1520364665926631</v>
       </c>
       <c r="T52">
-        <v>2.410386370703323</v>
+        <v>2.453498073733559</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.644203082060084</v>
+        <v>1.611963805941259</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1102998686304049</v>
+        <v>0.1104148723350829</v>
       </c>
       <c r="C53">
-        <v>319.6737814547996</v>
+        <v>308.1156214787471</v>
       </c>
       <c r="D53">
-        <v>788.9277814547996</v>
+        <v>787.5236214787471</v>
       </c>
       <c r="E53">
-        <v>126.354</v>
+        <v>136.508</v>
       </c>
       <c r="F53">
-        <v>517.854</v>
+        <v>528.008</v>
       </c>
       <c r="G53">
         <v>48.6</v>
@@ -5639,28 +5639,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M53">
-        <v>46.60686</v>
+        <v>47.52072</v>
       </c>
       <c r="N53">
-        <v>28.52171142857143</v>
+        <v>27.60785142857143</v>
       </c>
       <c r="O53">
-        <v>6.274776514285715</v>
+        <v>6.073727314285715</v>
       </c>
       <c r="P53">
-        <v>22.24693491428571</v>
+        <v>21.53412411428571</v>
       </c>
       <c r="Q53">
-        <v>68.54693491428571</v>
+        <v>67.83412411428571</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1520364665926631</v>
+        <v>0.1539809840314227</v>
       </c>
       <c r="T53">
-        <v>2.453498073733559</v>
+        <v>2.498406097723388</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.611963805941259</v>
+        <v>1.58096450198085</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1104148723350829</v>
+        <v>0.1105298760397609</v>
       </c>
       <c r="C54">
-        <v>308.1156214787471</v>
+        <v>296.5624509637927</v>
       </c>
       <c r="D54">
-        <v>787.5236214787471</v>
+        <v>786.1244509637927</v>
       </c>
       <c r="E54">
-        <v>136.508</v>
+        <v>146.662</v>
       </c>
       <c r="F54">
-        <v>528.008</v>
+        <v>538.162</v>
       </c>
       <c r="G54">
         <v>48.6</v>
@@ -5721,28 +5721,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M54">
-        <v>47.52072</v>
+        <v>48.43458</v>
       </c>
       <c r="N54">
-        <v>27.60785142857143</v>
+        <v>26.69399142857143</v>
       </c>
       <c r="O54">
-        <v>6.073727314285715</v>
+        <v>5.872678114285715</v>
       </c>
       <c r="P54">
-        <v>21.53412411428571</v>
+        <v>20.82131331428571</v>
       </c>
       <c r="Q54">
-        <v>67.83412411428571</v>
+        <v>67.12131331428571</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1539809840314227</v>
+        <v>0.1560082468931082</v>
       </c>
       <c r="T54">
-        <v>2.498406097723388</v>
+        <v>2.545225101457465</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.58096450198085</v>
+        <v>1.551134983075551</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1105298760397609</v>
+        <v>0.1106448797444388</v>
       </c>
       <c r="C55">
-        <v>296.5624509637927</v>
+        <v>285.0142433632068</v>
       </c>
       <c r="D55">
-        <v>786.1244509637927</v>
+        <v>784.7302433632068</v>
       </c>
       <c r="E55">
-        <v>146.662</v>
+        <v>156.816</v>
       </c>
       <c r="F55">
-        <v>538.162</v>
+        <v>548.316</v>
       </c>
       <c r="G55">
         <v>48.6</v>
@@ -5803,28 +5803,28 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M55">
-        <v>48.43458</v>
+        <v>49.34844</v>
       </c>
       <c r="N55">
-        <v>26.69399142857143</v>
+        <v>25.78013142857143</v>
       </c>
       <c r="O55">
-        <v>5.872678114285715</v>
+        <v>5.671628914285715</v>
       </c>
       <c r="P55">
-        <v>20.82131331428571</v>
+        <v>20.10850251428571</v>
       </c>
       <c r="Q55">
-        <v>67.12131331428571</v>
+        <v>66.40850251428571</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1560082468931082</v>
+        <v>0.1581236516183453</v>
       </c>
       <c r="T55">
-        <v>2.545225101457465</v>
+        <v>2.594079714049546</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.551134983075551</v>
+        <v>1.522410261166744</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1106448797444388</v>
+        <v>0.1372054855381348</v>
       </c>
       <c r="C56">
-        <v>285.0142433632068</v>
+        <v>46.83333091203372</v>
       </c>
       <c r="D56">
-        <v>784.7302433632068</v>
+        <v>556.7033309120337</v>
       </c>
       <c r="E56">
-        <v>156.816</v>
+        <v>166.97</v>
       </c>
       <c r="F56">
-        <v>548.316</v>
+        <v>558.47</v>
       </c>
       <c r="G56">
         <v>48.6</v>
@@ -5885,45 +5885,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M56">
-        <v>49.34844</v>
+        <v>81.98339600000001</v>
       </c>
       <c r="N56">
-        <v>25.78013142857143</v>
+        <v>-6.85482457142858</v>
       </c>
       <c r="O56">
-        <v>5.671628914285715</v>
+        <v>-1.508061405714288</v>
       </c>
       <c r="P56">
-        <v>20.10850251428571</v>
+        <v>-5.346763165714292</v>
       </c>
       <c r="Q56">
-        <v>66.40850251428571</v>
+        <v>40.9532368342857</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1581236516183453</v>
+        <v>0.1616513245567325</v>
       </c>
       <c r="T56">
-        <v>2.594079714049546</v>
+        <v>2.675550220709758</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.22</v>
+        <v>0.2016052825414272</v>
       </c>
       <c r="W56">
-        <v>0.0702</v>
+        <v>0.1172043445229185</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.522410261166744</v>
+        <v>0.9163876479155781</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1372054855381348</v>
+        <v>0.1382154855381348</v>
       </c>
       <c r="C57">
-        <v>46.83333091203372</v>
+        <v>30.59517346864595</v>
       </c>
       <c r="D57">
-        <v>556.7033309120337</v>
+        <v>550.619173468646</v>
       </c>
       <c r="E57">
-        <v>166.97</v>
+        <v>177.124</v>
       </c>
       <c r="F57">
-        <v>558.47</v>
+        <v>568.624</v>
       </c>
       <c r="G57">
         <v>48.6</v>
@@ -5967,37 +5967,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M57">
-        <v>81.98339600000001</v>
+        <v>83.47400320000001</v>
       </c>
       <c r="N57">
-        <v>-6.85482457142858</v>
+        <v>-8.345431771428579</v>
       </c>
       <c r="O57">
-        <v>-1.508061405714288</v>
+        <v>-1.835994989714288</v>
       </c>
       <c r="P57">
-        <v>-5.346763165714292</v>
+        <v>-6.509436781714292</v>
       </c>
       <c r="Q57">
-        <v>40.9532368342857</v>
+        <v>39.7905632182857</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1616513245567325</v>
+        <v>0.1642843092057491</v>
       </c>
       <c r="T57">
-        <v>2.675550220709758</v>
+        <v>2.736358180271343</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2016052825414272</v>
+        <v>0.1980051882103303</v>
       </c>
       <c r="W57">
-        <v>0.1172043445229185</v>
+        <v>0.1177328383707235</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9163876479155781</v>
+        <v>0.9000235827742286</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1382154855381348</v>
+        <v>0.1392254855381348</v>
       </c>
       <c r="C58">
-        <v>30.59517346864595</v>
+        <v>14.48856469171494</v>
       </c>
       <c r="D58">
-        <v>550.619173468646</v>
+        <v>544.6665646917149</v>
       </c>
       <c r="E58">
-        <v>177.124</v>
+        <v>187.278</v>
       </c>
       <c r="F58">
-        <v>568.624</v>
+        <v>578.778</v>
       </c>
       <c r="G58">
         <v>48.6</v>
@@ -6049,37 +6049,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M58">
-        <v>83.47400320000001</v>
+        <v>84.96461040000001</v>
       </c>
       <c r="N58">
-        <v>-8.345431771428579</v>
+        <v>-9.836038971428579</v>
       </c>
       <c r="O58">
-        <v>-1.835994989714288</v>
+        <v>-2.163928573714287</v>
       </c>
       <c r="P58">
-        <v>-6.509436781714292</v>
+        <v>-7.672110397714292</v>
       </c>
       <c r="Q58">
-        <v>39.7905632182857</v>
+        <v>38.62788960228571</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1642843092057491</v>
+        <v>0.1670397582570456</v>
       </c>
       <c r="T58">
-        <v>2.736358180271343</v>
+        <v>2.79999441702184</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1980051882103303</v>
+        <v>0.1945314129785701</v>
       </c>
       <c r="W58">
-        <v>0.1177328383707235</v>
+        <v>0.1182427885747459</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9000235827742286</v>
+        <v>0.8842336953571368</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1392254855381348</v>
+        <v>0.1402354855381348</v>
       </c>
       <c r="C59">
-        <v>14.48856469171494</v>
+        <v>-1.49071620988525</v>
       </c>
       <c r="D59">
-        <v>544.6665646917149</v>
+        <v>538.8412837901147</v>
       </c>
       <c r="E59">
-        <v>187.278</v>
+        <v>197.432</v>
       </c>
       <c r="F59">
-        <v>578.778</v>
+        <v>588.932</v>
       </c>
       <c r="G59">
         <v>48.6</v>
@@ -6131,37 +6131,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M59">
-        <v>84.96461040000001</v>
+        <v>86.45521760000001</v>
       </c>
       <c r="N59">
-        <v>-9.836038971428579</v>
+        <v>-11.32664617142858</v>
       </c>
       <c r="O59">
-        <v>-2.163928573714287</v>
+        <v>-2.491862157714287</v>
       </c>
       <c r="P59">
-        <v>-7.672110397714292</v>
+        <v>-8.834784013714291</v>
       </c>
       <c r="Q59">
-        <v>38.62788960228571</v>
+        <v>37.46521598628571</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1670397582570456</v>
+        <v>0.1699264191679277</v>
       </c>
       <c r="T59">
-        <v>2.79999441702184</v>
+        <v>2.866660950760456</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1945314129785701</v>
+        <v>0.1911774230996292</v>
       </c>
       <c r="W59">
-        <v>0.1182427885747459</v>
+        <v>0.1187351542889744</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8842336953571368</v>
+        <v>0.8689882868164966</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1402354855381348</v>
+        <v>0.1412454855381348</v>
       </c>
       <c r="C60">
-        <v>-1.490716209884908</v>
+        <v>-17.34671137036412</v>
       </c>
       <c r="D60">
-        <v>538.841283790115</v>
+        <v>533.1392886296358</v>
       </c>
       <c r="E60">
-        <v>197.4319999999999</v>
+        <v>207.5859999999999</v>
       </c>
       <c r="F60">
-        <v>588.9319999999999</v>
+        <v>599.0859999999999</v>
       </c>
       <c r="G60">
         <v>48.6</v>
@@ -6213,37 +6213,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M60">
-        <v>86.4552176</v>
+        <v>87.9458248</v>
       </c>
       <c r="N60">
-        <v>-11.32664617142856</v>
+        <v>-12.81725337142856</v>
       </c>
       <c r="O60">
-        <v>-2.491862157714284</v>
+        <v>-2.819795741714284</v>
       </c>
       <c r="P60">
-        <v>-8.83478401371428</v>
+        <v>-9.99745762971428</v>
       </c>
       <c r="Q60">
-        <v>37.46521598628571</v>
+        <v>36.30254237028572</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1699264191679276</v>
+        <v>0.1729538928061698</v>
       </c>
       <c r="T60">
-        <v>2.866660950760454</v>
+        <v>2.9365795105351</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1911774230996293</v>
+        <v>0.1879371277928559</v>
       </c>
       <c r="W60">
-        <v>0.1187351542889744</v>
+        <v>0.1192108296400088</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8689882868164968</v>
+        <v>0.8542596717857087</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1412454855381348</v>
+        <v>0.1422554855381348</v>
       </c>
       <c r="C61">
-        <v>-17.34671137036412</v>
+        <v>-33.08329362073334</v>
       </c>
       <c r="D61">
-        <v>533.1392886296358</v>
+        <v>527.5567063792666</v>
       </c>
       <c r="E61">
-        <v>207.5859999999999</v>
+        <v>217.74</v>
       </c>
       <c r="F61">
-        <v>599.0859999999999</v>
+        <v>609.24</v>
       </c>
       <c r="G61">
         <v>48.6</v>
@@ -6295,37 +6295,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M61">
-        <v>87.9458248</v>
+        <v>89.43643200000001</v>
       </c>
       <c r="N61">
-        <v>-12.81725337142856</v>
+        <v>-14.30786057142858</v>
       </c>
       <c r="O61">
-        <v>-2.819795741714284</v>
+        <v>-3.147729325714287</v>
       </c>
       <c r="P61">
-        <v>-9.99745762971428</v>
+        <v>-11.16013124571429</v>
       </c>
       <c r="Q61">
-        <v>36.30254237028572</v>
+        <v>35.13986875428571</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1729538928061698</v>
+        <v>0.176132740126324</v>
       </c>
       <c r="T61">
-        <v>2.9365795105351</v>
+        <v>3.009993998298477</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1879371277928559</v>
+        <v>0.1848048423296416</v>
       </c>
       <c r="W61">
-        <v>0.1192108296400088</v>
+        <v>0.1196706491460086</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8542596717857087</v>
+        <v>0.8400220105892801</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1422554855381348</v>
+        <v>0.1432654855381348</v>
       </c>
       <c r="C62">
-        <v>-33.08329362073334</v>
+        <v>-48.7041752609482</v>
       </c>
       <c r="D62">
-        <v>527.5567063792666</v>
+        <v>522.0898247390518</v>
       </c>
       <c r="E62">
-        <v>217.74</v>
+        <v>227.894</v>
       </c>
       <c r="F62">
-        <v>609.24</v>
+        <v>619.394</v>
       </c>
       <c r="G62">
         <v>48.6</v>
@@ -6377,37 +6377,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M62">
-        <v>89.43643200000001</v>
+        <v>90.92703920000001</v>
       </c>
       <c r="N62">
-        <v>-14.30786057142858</v>
+        <v>-15.79846777142858</v>
       </c>
       <c r="O62">
-        <v>-3.147729325714287</v>
+        <v>-3.475662909714287</v>
       </c>
       <c r="P62">
-        <v>-11.16013124571429</v>
+        <v>-12.32280486171429</v>
       </c>
       <c r="Q62">
-        <v>35.13986875428571</v>
+        <v>33.97719513828571</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.176132740126324</v>
+        <v>0.1794746052577683</v>
       </c>
       <c r="T62">
-        <v>3.009993998298477</v>
+        <v>3.087173331588182</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1848048423296416</v>
+        <v>0.1817752547504672</v>
       </c>
       <c r="W62">
-        <v>0.1196706491460086</v>
+        <v>0.1201153926026314</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8400220105892801</v>
+        <v>0.8262511579566689</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1432654855381348</v>
+        <v>0.1442754855381348</v>
       </c>
       <c r="C63">
-        <v>-48.7041752609482</v>
+        <v>-64.21291629223003</v>
       </c>
       <c r="D63">
-        <v>522.0898247390518</v>
+        <v>516.7350837077699</v>
       </c>
       <c r="E63">
-        <v>227.894</v>
+        <v>238.048</v>
       </c>
       <c r="F63">
-        <v>619.394</v>
+        <v>629.548</v>
       </c>
       <c r="G63">
         <v>48.6</v>
@@ -6459,37 +6459,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M63">
-        <v>90.92703920000001</v>
+        <v>92.41764640000001</v>
       </c>
       <c r="N63">
-        <v>-15.79846777142858</v>
+        <v>-17.28907497142858</v>
       </c>
       <c r="O63">
-        <v>-3.475662909714287</v>
+        <v>-3.803596493714287</v>
       </c>
       <c r="P63">
-        <v>-12.32280486171429</v>
+        <v>-13.48547847771429</v>
       </c>
       <c r="Q63">
-        <v>33.97719513828571</v>
+        <v>32.81452152228571</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1794746052577683</v>
+        <v>0.1829923580277095</v>
       </c>
       <c r="T63">
-        <v>3.087173331588182</v>
+        <v>3.168414735051029</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1817752547504672</v>
+        <v>0.178843395802879</v>
       </c>
       <c r="W63">
-        <v>0.1201153926026314</v>
+        <v>0.1205457894961374</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8262511579566689</v>
+        <v>0.8129245263767226</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1442754855381348</v>
+        <v>0.1452854855381348</v>
       </c>
       <c r="C64">
-        <v>-64.21291629223003</v>
+        <v>-79.61293214792784</v>
       </c>
       <c r="D64">
-        <v>516.7350837077699</v>
+        <v>511.4890678520721</v>
       </c>
       <c r="E64">
-        <v>238.048</v>
+        <v>248.202</v>
       </c>
       <c r="F64">
-        <v>629.548</v>
+        <v>639.702</v>
       </c>
       <c r="G64">
         <v>48.6</v>
@@ -6541,37 +6541,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M64">
-        <v>92.41764640000001</v>
+        <v>93.90825360000001</v>
       </c>
       <c r="N64">
-        <v>-17.28907497142858</v>
+        <v>-18.77968217142858</v>
       </c>
       <c r="O64">
-        <v>-3.803596493714287</v>
+        <v>-4.131530077714286</v>
       </c>
       <c r="P64">
-        <v>-13.48547847771429</v>
+        <v>-14.64815209371429</v>
       </c>
       <c r="Q64">
-        <v>32.81452152228571</v>
+        <v>31.65184790628571</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1829923580277095</v>
+        <v>0.186700259596026</v>
       </c>
       <c r="T64">
-        <v>3.168414735051029</v>
+        <v>3.254047565728084</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.178843395802879</v>
+        <v>0.1760046117425158</v>
       </c>
       <c r="W64">
-        <v>0.1205457894961374</v>
+        <v>0.1209625229961987</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8129245263767226</v>
+        <v>0.800020962465981</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1452854855381348</v>
+        <v>0.1826039193858943</v>
       </c>
       <c r="C65">
-        <v>-79.61293214792784</v>
+        <v>-229.2948859388327</v>
       </c>
       <c r="D65">
-        <v>511.4890678520721</v>
+        <v>371.9611140611673</v>
       </c>
       <c r="E65">
-        <v>248.202</v>
+        <v>258.356</v>
       </c>
       <c r="F65">
-        <v>639.702</v>
+        <v>649.856</v>
       </c>
       <c r="G65">
         <v>48.6</v>
@@ -6623,45 +6623,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M65">
-        <v>93.90825360000001</v>
+        <v>130.4910848</v>
       </c>
       <c r="N65">
-        <v>-18.77968217142858</v>
+        <v>-55.36251337142858</v>
       </c>
       <c r="O65">
-        <v>-4.131530077714286</v>
+        <v>-12.17975294171429</v>
       </c>
       <c r="P65">
-        <v>-14.64815209371429</v>
+        <v>-43.18276042971429</v>
       </c>
       <c r="Q65">
-        <v>31.65184790628571</v>
+        <v>3.117239570285705</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.186700259596026</v>
+        <v>0.1954709163841365</v>
       </c>
       <c r="T65">
-        <v>3.254047565728084</v>
+        <v>3.456603149749112</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1760046117425158</v>
+        <v>0.1266621833945066</v>
       </c>
       <c r="W65">
-        <v>0.1209625229961987</v>
+        <v>0.1753662335743831</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.800020962465981</v>
+        <v>0.5757371972477574</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1826039193858943</v>
+        <v>0.1841539193858943</v>
       </c>
       <c r="C66">
-        <v>-229.2948859388327</v>
+        <v>-243.6160228681938</v>
       </c>
       <c r="D66">
-        <v>371.9611140611673</v>
+        <v>367.7939771318062</v>
       </c>
       <c r="E66">
-        <v>258.356</v>
+        <v>268.51</v>
       </c>
       <c r="F66">
-        <v>649.856</v>
+        <v>660.01</v>
       </c>
       <c r="G66">
         <v>48.6</v>
@@ -6705,37 +6705,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M66">
-        <v>130.4910848</v>
+        <v>132.530008</v>
       </c>
       <c r="N66">
-        <v>-55.36251337142858</v>
+        <v>-57.40143657142858</v>
       </c>
       <c r="O66">
-        <v>-12.17975294171429</v>
+        <v>-12.62831604571429</v>
       </c>
       <c r="P66">
-        <v>-43.18276042971429</v>
+        <v>-44.77312052571429</v>
       </c>
       <c r="Q66">
-        <v>3.117239570285705</v>
+        <v>1.526879474285707</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1954709163841365</v>
+        <v>0.1997472282808262</v>
       </c>
       <c r="T66">
-        <v>3.456603149749112</v>
+        <v>3.555363239741944</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1266621833945066</v>
+        <v>0.1247135344192065</v>
       </c>
       <c r="W66">
-        <v>0.1753662335743831</v>
+        <v>0.1757575222886233</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5757371972477574</v>
+        <v>0.5668797019054841</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1841539193858943</v>
+        <v>0.1857039193858943</v>
       </c>
       <c r="C67">
-        <v>-243.6160228681938</v>
+        <v>-257.8448241107655</v>
       </c>
       <c r="D67">
-        <v>367.7939771318062</v>
+        <v>363.7191758892345</v>
       </c>
       <c r="E67">
-        <v>268.51</v>
+        <v>278.664</v>
       </c>
       <c r="F67">
-        <v>660.01</v>
+        <v>670.164</v>
       </c>
       <c r="G67">
         <v>48.6</v>
@@ -6787,37 +6787,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M67">
-        <v>132.530008</v>
+        <v>134.5689312</v>
       </c>
       <c r="N67">
-        <v>-57.40143657142858</v>
+        <v>-59.44035977142858</v>
       </c>
       <c r="O67">
-        <v>-12.62831604571429</v>
+        <v>-13.07687914971429</v>
       </c>
       <c r="P67">
-        <v>-44.77312052571429</v>
+        <v>-46.36348062171429</v>
       </c>
       <c r="Q67">
-        <v>1.526879474285707</v>
+        <v>-0.06348062171429092</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1997472282808262</v>
+        <v>0.2042750879361446</v>
       </c>
       <c r="T67">
-        <v>3.555363239741944</v>
+        <v>3.659932746793178</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1247135344192065</v>
+        <v>0.1228239354128549</v>
       </c>
       <c r="W67">
-        <v>0.1757575222886233</v>
+        <v>0.1761369537690987</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5668797019054841</v>
+        <v>0.5582906155129768</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1857039193858943</v>
+        <v>0.1872539193858943</v>
       </c>
       <c r="C68">
-        <v>-257.8448241107655</v>
+        <v>-271.9843250079894</v>
       </c>
       <c r="D68">
-        <v>363.7191758892345</v>
+        <v>359.7336749920105</v>
       </c>
       <c r="E68">
-        <v>278.664</v>
+        <v>288.818</v>
       </c>
       <c r="F68">
-        <v>670.164</v>
+        <v>680.318</v>
       </c>
       <c r="G68">
         <v>48.6</v>
@@ -6869,37 +6869,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M68">
-        <v>134.5689312</v>
+        <v>136.6078544</v>
       </c>
       <c r="N68">
-        <v>-59.44035977142858</v>
+        <v>-61.47928297142857</v>
       </c>
       <c r="O68">
-        <v>-13.07687914971429</v>
+        <v>-13.52544225371429</v>
       </c>
       <c r="P68">
-        <v>-46.36348062171429</v>
+        <v>-47.95384071771429</v>
       </c>
       <c r="Q68">
-        <v>-0.06348062171429092</v>
+        <v>-1.653840717714289</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2042750879361446</v>
+        <v>0.209077363328149</v>
       </c>
       <c r="T68">
-        <v>3.659932746793178</v>
+        <v>3.770839799726305</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1228239354128549</v>
+        <v>0.1209907423469914</v>
       </c>
       <c r="W68">
-        <v>0.1761369537690987</v>
+        <v>0.1765050589367241</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5582906155129768</v>
+        <v>0.5499579197590518</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1872539193858943</v>
+        <v>0.1888039193858943</v>
       </c>
       <c r="C69">
-        <v>-271.9843250079894</v>
+        <v>-286.0374293026973</v>
       </c>
       <c r="D69">
-        <v>359.7336749920105</v>
+        <v>355.8345706973026</v>
       </c>
       <c r="E69">
-        <v>288.818</v>
+        <v>298.972</v>
       </c>
       <c r="F69">
-        <v>680.318</v>
+        <v>690.472</v>
       </c>
       <c r="G69">
         <v>48.6</v>
@@ -6951,37 +6951,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M69">
-        <v>136.6078544</v>
+        <v>138.6467776</v>
       </c>
       <c r="N69">
-        <v>-61.47928297142857</v>
+        <v>-63.51820617142857</v>
       </c>
       <c r="O69">
-        <v>-13.52544225371429</v>
+        <v>-13.97400535771429</v>
       </c>
       <c r="P69">
-        <v>-47.95384071771429</v>
+        <v>-49.54420081371428</v>
       </c>
       <c r="Q69">
-        <v>-1.653840717714289</v>
+        <v>-3.244200813714286</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.209077363328149</v>
+        <v>0.2141797809321536</v>
       </c>
       <c r="T69">
-        <v>3.770839799726305</v>
+        <v>3.888678543467752</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1209907423469914</v>
+        <v>0.1192114667242415</v>
       </c>
       <c r="W69">
-        <v>0.1765050589367241</v>
+        <v>0.1768623374817723</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5499579197590518</v>
+        <v>0.5418703032920069</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1888039193858943</v>
+        <v>0.1903539193858943</v>
       </c>
       <c r="C70">
-        <v>-286.0374293026973</v>
+        <v>-300.0069161945364</v>
       </c>
       <c r="D70">
-        <v>355.8345706973026</v>
+        <v>352.0190838054637</v>
       </c>
       <c r="E70">
-        <v>298.972</v>
+        <v>309.1260000000001</v>
       </c>
       <c r="F70">
-        <v>690.472</v>
+        <v>700.6260000000001</v>
       </c>
       <c r="G70">
         <v>48.6</v>
@@ -7033,37 +7033,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M70">
-        <v>138.6467776</v>
+        <v>140.6857008</v>
       </c>
       <c r="N70">
-        <v>-63.51820617142857</v>
+        <v>-65.5571293714286</v>
       </c>
       <c r="O70">
-        <v>-13.97400535771429</v>
+        <v>-14.42256846171429</v>
       </c>
       <c r="P70">
-        <v>-49.54420081371428</v>
+        <v>-51.13456090971431</v>
       </c>
       <c r="Q70">
-        <v>-3.244200813714286</v>
+        <v>-4.834560909714313</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2141797809321536</v>
+        <v>0.2196113867686747</v>
       </c>
       <c r="T70">
-        <v>3.888678543467752</v>
+        <v>4.014119786805422</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1192114667242415</v>
+        <v>0.1174837643079481</v>
       </c>
       <c r="W70">
-        <v>0.1768623374817723</v>
+        <v>0.177209260126964</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5418703032920069</v>
+        <v>0.5340171104906734</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1903539193858943</v>
+        <v>0.1919039193858943</v>
       </c>
       <c r="C71">
-        <v>-300.0069161945364</v>
+        <v>-313.8954469462907</v>
       </c>
       <c r="D71">
-        <v>352.0190838054637</v>
+        <v>348.2845530537093</v>
       </c>
       <c r="E71">
-        <v>309.1260000000001</v>
+        <v>319.2800000000001</v>
       </c>
       <c r="F71">
-        <v>700.6260000000001</v>
+        <v>710.7800000000001</v>
       </c>
       <c r="G71">
         <v>48.6</v>
@@ -7115,37 +7115,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M71">
-        <v>140.6857008</v>
+        <v>142.724624</v>
       </c>
       <c r="N71">
-        <v>-65.5571293714286</v>
+        <v>-67.5960525714286</v>
       </c>
       <c r="O71">
-        <v>-14.42256846171429</v>
+        <v>-14.87113156571429</v>
       </c>
       <c r="P71">
-        <v>-51.13456090971431</v>
+        <v>-52.72492100571431</v>
       </c>
       <c r="Q71">
-        <v>-4.834560909714313</v>
+        <v>-6.42492100571431</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2196113867686747</v>
+        <v>0.2254050996609639</v>
       </c>
       <c r="T71">
-        <v>4.014119786805422</v>
+        <v>4.147923779698935</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1174837643079481</v>
+        <v>0.1158054248178346</v>
       </c>
       <c r="W71">
-        <v>0.177209260126964</v>
+        <v>0.1775462706965788</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5340171104906734</v>
+        <v>0.5263882946265208</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1919039193858943</v>
+        <v>0.1934539193858943</v>
       </c>
       <c r="C72">
-        <v>-313.8954469462907</v>
+        <v>-327.705571074106</v>
       </c>
       <c r="D72">
-        <v>348.2845530537093</v>
+        <v>344.628428925894</v>
       </c>
       <c r="E72">
-        <v>319.2800000000001</v>
+        <v>329.4340000000001</v>
       </c>
       <c r="F72">
-        <v>710.7800000000001</v>
+        <v>720.9340000000001</v>
       </c>
       <c r="G72">
         <v>48.6</v>
@@ -7197,37 +7197,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M72">
-        <v>142.724624</v>
+        <v>144.7635472</v>
       </c>
       <c r="N72">
-        <v>-67.5960525714286</v>
+        <v>-69.6349757714286</v>
       </c>
       <c r="O72">
-        <v>-14.87113156571429</v>
+        <v>-15.31969466971429</v>
       </c>
       <c r="P72">
-        <v>-52.72492100571431</v>
+        <v>-54.31528110171431</v>
       </c>
       <c r="Q72">
-        <v>-6.42492100571431</v>
+        <v>-8.015281101714308</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2254050996609639</v>
+        <v>0.2315983789596178</v>
       </c>
       <c r="T72">
-        <v>4.147923779698935</v>
+        <v>4.290955634171312</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1158054248178346</v>
+        <v>0.1141743624964567</v>
       </c>
       <c r="W72">
-        <v>0.1775462706965788</v>
+        <v>0.1778737880107115</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5263882946265208</v>
+        <v>0.5189743749838939</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1934539193858943</v>
+        <v>0.1950039193858943</v>
       </c>
       <c r="C73">
-        <v>-327.7055710741059</v>
+        <v>-341.4397321518693</v>
       </c>
       <c r="D73">
-        <v>344.628428925894</v>
+        <v>341.0482678481306</v>
       </c>
       <c r="E73">
-        <v>329.434</v>
+        <v>339.588</v>
       </c>
       <c r="F73">
-        <v>720.934</v>
+        <v>731.088</v>
       </c>
       <c r="G73">
         <v>48.6</v>
@@ -7279,37 +7279,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M73">
-        <v>144.7635472</v>
+        <v>146.8024704</v>
       </c>
       <c r="N73">
-        <v>-69.63497577142857</v>
+        <v>-71.67389897142857</v>
       </c>
       <c r="O73">
-        <v>-15.31969466971429</v>
+        <v>-15.76825777371429</v>
       </c>
       <c r="P73">
-        <v>-54.31528110171428</v>
+        <v>-55.90564119771429</v>
       </c>
       <c r="Q73">
-        <v>-8.015281101714287</v>
+        <v>-9.605641197714291</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2315983789596177</v>
+        <v>0.2382340353510327</v>
       </c>
       <c r="T73">
-        <v>4.290955634171311</v>
+        <v>4.444204049677429</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1141743624964567</v>
+        <v>0.1125886074617837</v>
       </c>
       <c r="W73">
-        <v>0.1778737880107115</v>
+        <v>0.1781922076216738</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.518974374983894</v>
+        <v>0.511766397553562</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1950039193858943</v>
+        <v>0.1965539193858943</v>
       </c>
       <c r="C74">
-        <v>-341.4397321518693</v>
+        <v>-355.1002732575201</v>
       </c>
       <c r="D74">
-        <v>341.0482678481306</v>
+        <v>337.5417267424798</v>
       </c>
       <c r="E74">
-        <v>339.588</v>
+        <v>349.742</v>
       </c>
       <c r="F74">
-        <v>731.088</v>
+        <v>741.242</v>
       </c>
       <c r="G74">
         <v>48.6</v>
@@ -7361,37 +7361,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M74">
-        <v>146.8024704</v>
+        <v>148.8413936</v>
       </c>
       <c r="N74">
-        <v>-71.67389897142857</v>
+        <v>-73.71282217142857</v>
       </c>
       <c r="O74">
-        <v>-15.76825777371429</v>
+        <v>-16.21682087771429</v>
       </c>
       <c r="P74">
-        <v>-55.90564119771429</v>
+        <v>-57.49600129371429</v>
       </c>
       <c r="Q74">
-        <v>-9.605641197714291</v>
+        <v>-11.19600129371429</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2382340353510327</v>
+        <v>0.2453612218455154</v>
       </c>
       <c r="T74">
-        <v>4.444204049677429</v>
+        <v>4.608804199665482</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1125886074617837</v>
+        <v>0.1110462977705264</v>
       </c>
       <c r="W74">
-        <v>0.1781922076216738</v>
+        <v>0.1785019034076783</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.511766397553562</v>
+        <v>0.504755898956938</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1965539193858943</v>
+        <v>0.2247094335622042</v>
       </c>
       <c r="C75">
-        <v>-355.1002732575201</v>
+        <v>-418.3742272094716</v>
       </c>
       <c r="D75">
-        <v>337.5417267424798</v>
+        <v>284.4217727905283</v>
       </c>
       <c r="E75">
-        <v>349.742</v>
+        <v>359.896</v>
       </c>
       <c r="F75">
-        <v>741.242</v>
+        <v>751.396</v>
       </c>
       <c r="G75">
         <v>48.6</v>
@@ -7443,45 +7443,45 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M75">
-        <v>148.8413936</v>
+        <v>177.1791768</v>
       </c>
       <c r="N75">
-        <v>-73.71282217142857</v>
+        <v>-102.0506053714286</v>
       </c>
       <c r="O75">
-        <v>-16.21682087771429</v>
+        <v>-22.45113318171428</v>
       </c>
       <c r="P75">
-        <v>-57.49600129371429</v>
+        <v>-79.59947218971428</v>
       </c>
       <c r="Q75">
-        <v>-11.19600129371429</v>
+        <v>-33.29947218971428</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2453612218455154</v>
+        <v>0.2557501695176884</v>
       </c>
       <c r="T75">
-        <v>4.608804199665482</v>
+        <v>4.848733707105969</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1110462977705264</v>
+        <v>0.09328571230999035</v>
       </c>
       <c r="W75">
-        <v>0.1785019034076783</v>
+        <v>0.2138032290373043</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.504755898956938</v>
+        <v>0.4240259650454107</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2247094335622042</v>
+        <v>0.2266094335622041</v>
       </c>
       <c r="C76">
-        <v>-418.3742272094716</v>
+        <v>-431.5170168851831</v>
       </c>
       <c r="D76">
-        <v>284.4217727905283</v>
+        <v>281.4329831148168</v>
       </c>
       <c r="E76">
-        <v>359.896</v>
+        <v>370.05</v>
       </c>
       <c r="F76">
-        <v>751.396</v>
+        <v>761.55</v>
       </c>
       <c r="G76">
         <v>48.6</v>
@@ -7525,37 +7525,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M76">
-        <v>177.1791768</v>
+        <v>179.57349</v>
       </c>
       <c r="N76">
-        <v>-102.0506053714286</v>
+        <v>-104.4449185714286</v>
       </c>
       <c r="O76">
-        <v>-22.45113318171428</v>
+        <v>-22.97788208571428</v>
       </c>
       <c r="P76">
-        <v>-79.59947218971428</v>
+        <v>-81.46703648571427</v>
       </c>
       <c r="Q76">
-        <v>-33.29947218971428</v>
+        <v>-35.16703648571428</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2557501695176884</v>
+        <v>0.264148176298396</v>
       </c>
       <c r="T76">
-        <v>4.848733707105969</v>
+        <v>5.042683055390208</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09328571230999035</v>
+        <v>0.09204190281252381</v>
       </c>
       <c r="W76">
-        <v>0.2138032290373043</v>
+        <v>0.2140965193168069</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4240259650454107</v>
+        <v>0.4183722855114719</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2266094335622041</v>
+        <v>0.2285094335622042</v>
       </c>
       <c r="C77">
-        <v>-431.5170168851831</v>
+        <v>-444.5976455627117</v>
       </c>
       <c r="D77">
-        <v>281.4329831148168</v>
+        <v>278.5063544372882</v>
       </c>
       <c r="E77">
-        <v>370.05</v>
+        <v>380.204</v>
       </c>
       <c r="F77">
-        <v>761.55</v>
+        <v>771.704</v>
       </c>
       <c r="G77">
         <v>48.6</v>
@@ -7607,37 +7607,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M77">
-        <v>179.57349</v>
+        <v>181.9678032</v>
       </c>
       <c r="N77">
-        <v>-104.4449185714286</v>
+        <v>-106.8392317714286</v>
       </c>
       <c r="O77">
-        <v>-22.97788208571428</v>
+        <v>-23.50463098971428</v>
       </c>
       <c r="P77">
-        <v>-81.46703648571427</v>
+        <v>-83.33460078171427</v>
       </c>
       <c r="Q77">
-        <v>-35.16703648571428</v>
+        <v>-37.03460078171427</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.264148176298396</v>
+        <v>0.2732460169774958</v>
       </c>
       <c r="T77">
-        <v>5.042683055390208</v>
+        <v>5.2527948493648</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09204190281252381</v>
+        <v>0.09083082514393798</v>
       </c>
       <c r="W77">
-        <v>0.2140965193168069</v>
+        <v>0.2143820914310594</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4183722855114719</v>
+        <v>0.4128673870178998</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2285094335622042</v>
+        <v>0.2304094335622042</v>
       </c>
       <c r="C78">
-        <v>-444.5976455627117</v>
+        <v>-457.618032524744</v>
       </c>
       <c r="D78">
-        <v>278.5063544372882</v>
+        <v>275.639967475256</v>
       </c>
       <c r="E78">
-        <v>380.204</v>
+        <v>390.3579999999999</v>
       </c>
       <c r="F78">
-        <v>771.704</v>
+        <v>781.8579999999999</v>
       </c>
       <c r="G78">
         <v>48.6</v>
@@ -7689,37 +7689,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M78">
-        <v>181.9678032</v>
+        <v>184.3621164</v>
       </c>
       <c r="N78">
-        <v>-106.8392317714286</v>
+        <v>-109.2335449714286</v>
       </c>
       <c r="O78">
-        <v>-23.50463098971428</v>
+        <v>-24.03137989371428</v>
       </c>
       <c r="P78">
-        <v>-83.33460078171427</v>
+        <v>-85.20216507771427</v>
       </c>
       <c r="Q78">
-        <v>-37.03460078171427</v>
+        <v>-38.90216507771427</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2732460169774958</v>
+        <v>0.2831349742373869</v>
       </c>
       <c r="T78">
-        <v>5.2527948493648</v>
+        <v>5.481177234119791</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09083082514393798</v>
+        <v>0.08965120403817253</v>
       </c>
       <c r="W78">
-        <v>0.2143820914310594</v>
+        <v>0.2146602460877989</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4128673870178998</v>
+        <v>0.4075054729007843</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2304094335622042</v>
+        <v>0.2323094335622042</v>
       </c>
       <c r="C79">
-        <v>-457.618032524744</v>
+        <v>-470.5800188458668</v>
       </c>
       <c r="D79">
-        <v>275.639967475256</v>
+        <v>272.8319811541332</v>
       </c>
       <c r="E79">
-        <v>390.3579999999999</v>
+        <v>400.5120000000001</v>
       </c>
       <c r="F79">
-        <v>781.8579999999999</v>
+        <v>792.0120000000001</v>
       </c>
       <c r="G79">
         <v>48.6</v>
@@ -7771,37 +7771,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M79">
-        <v>184.3621164</v>
+        <v>186.7564296</v>
       </c>
       <c r="N79">
-        <v>-109.2335449714286</v>
+        <v>-111.6278581714286</v>
       </c>
       <c r="O79">
-        <v>-24.03137989371428</v>
+        <v>-24.55812879771429</v>
       </c>
       <c r="P79">
-        <v>-85.20216507771427</v>
+        <v>-87.0697293737143</v>
       </c>
       <c r="Q79">
-        <v>-38.90216507771427</v>
+        <v>-40.7697293737143</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2831349742373869</v>
+        <v>0.2939229276118135</v>
       </c>
       <c r="T79">
-        <v>5.481177234119791</v>
+        <v>5.730321653852508</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08965120403817253</v>
+        <v>0.08850182962742673</v>
       </c>
       <c r="W79">
-        <v>0.2146602460877989</v>
+        <v>0.2149312685738528</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4075054729007843</v>
+        <v>0.4022810437610306</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2323094335622042</v>
+        <v>0.2342094335622042</v>
       </c>
       <c r="C80">
-        <v>-470.5800188458668</v>
+        <v>-483.4853713359835</v>
       </c>
       <c r="D80">
-        <v>272.8319811541332</v>
+        <v>270.0806286640165</v>
       </c>
       <c r="E80">
-        <v>400.5120000000001</v>
+        <v>410.6660000000001</v>
       </c>
       <c r="F80">
-        <v>792.0120000000001</v>
+        <v>802.1660000000001</v>
       </c>
       <c r="G80">
         <v>48.6</v>
@@ -7853,37 +7853,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M80">
-        <v>186.7564296</v>
+        <v>189.1507428</v>
       </c>
       <c r="N80">
-        <v>-111.6278581714286</v>
+        <v>-114.0221713714286</v>
       </c>
       <c r="O80">
-        <v>-24.55812879771429</v>
+        <v>-25.08487770171429</v>
       </c>
       <c r="P80">
-        <v>-87.0697293737143</v>
+        <v>-88.93729366971429</v>
       </c>
       <c r="Q80">
-        <v>-40.7697293737143</v>
+        <v>-42.6372936697143</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2939229276118135</v>
+        <v>0.3057383051171381</v>
       </c>
       <c r="T80">
-        <v>5.730321653852508</v>
+        <v>6.003194113559772</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08850182962742673</v>
+        <v>0.08738155330302892</v>
       </c>
       <c r="W80">
-        <v>0.2149312685738528</v>
+        <v>0.2151954297311458</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4022810437610306</v>
+        <v>0.3971888786501314</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2342094335622042</v>
+        <v>0.2361094335622042</v>
       </c>
       <c r="C81">
-        <v>-483.4853713359835</v>
+        <v>-496.3357862475116</v>
       </c>
       <c r="D81">
-        <v>270.0806286640165</v>
+        <v>267.3842137524884</v>
       </c>
       <c r="E81">
-        <v>410.6660000000001</v>
+        <v>420.8200000000001</v>
       </c>
       <c r="F81">
-        <v>802.1660000000001</v>
+        <v>812.3200000000001</v>
       </c>
       <c r="G81">
         <v>48.6</v>
@@ -7935,37 +7935,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M81">
-        <v>189.1507428</v>
+        <v>191.545056</v>
       </c>
       <c r="N81">
-        <v>-114.0221713714286</v>
+        <v>-116.4164845714286</v>
       </c>
       <c r="O81">
-        <v>-25.08487770171429</v>
+        <v>-25.61162660571429</v>
       </c>
       <c r="P81">
-        <v>-88.93729366971429</v>
+        <v>-90.80485796571429</v>
       </c>
       <c r="Q81">
-        <v>-42.6372936697143</v>
+        <v>-44.50485796571429</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3057383051171381</v>
+        <v>0.318735220372995</v>
       </c>
       <c r="T81">
-        <v>6.003194113559772</v>
+        <v>6.303353819237761</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08738155330302892</v>
+        <v>0.08628928388674106</v>
       </c>
       <c r="W81">
-        <v>0.2151954297311458</v>
+        <v>0.2154529868595065</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3971888786501314</v>
+        <v>0.3922240176670048</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2361094335622042</v>
+        <v>0.2380094335622042</v>
       </c>
       <c r="C82">
-        <v>-496.3357862475116</v>
+        <v>-509.1328927627041</v>
       </c>
       <c r="D82">
-        <v>267.3842137524884</v>
+        <v>264.7411072372959</v>
       </c>
       <c r="E82">
-        <v>420.8200000000001</v>
+        <v>430.974</v>
       </c>
       <c r="F82">
-        <v>812.3200000000001</v>
+        <v>822.474</v>
       </c>
       <c r="G82">
         <v>48.6</v>
@@ -8017,37 +8017,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M82">
-        <v>191.545056</v>
+        <v>193.9393692</v>
       </c>
       <c r="N82">
-        <v>-116.4164845714286</v>
+        <v>-118.8107977714286</v>
       </c>
       <c r="O82">
-        <v>-25.61162660571429</v>
+        <v>-26.13837550971429</v>
       </c>
       <c r="P82">
-        <v>-90.80485796571429</v>
+        <v>-92.6724222617143</v>
       </c>
       <c r="Q82">
-        <v>-44.50485796571429</v>
+        <v>-46.37242226171431</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.318735220372995</v>
+        <v>0.3331002319715737</v>
       </c>
       <c r="T82">
-        <v>6.303353819237761</v>
+        <v>6.635109283408169</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08628928388674106</v>
+        <v>0.08522398408567018</v>
       </c>
       <c r="W82">
-        <v>0.2154529868595065</v>
+        <v>0.215704184552599</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3922240176670048</v>
+        <v>0.3873817458439553</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2380094335622042</v>
+        <v>0.2399094335622042</v>
       </c>
       <c r="C83">
-        <v>-509.1328927627041</v>
+        <v>-521.878256276161</v>
       </c>
       <c r="D83">
-        <v>264.7411072372959</v>
+        <v>262.149743723839</v>
       </c>
       <c r="E83">
-        <v>430.974</v>
+        <v>441.128</v>
       </c>
       <c r="F83">
-        <v>822.474</v>
+        <v>832.628</v>
       </c>
       <c r="G83">
         <v>48.6</v>
@@ -8099,37 +8099,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M83">
-        <v>193.9393692</v>
+        <v>196.3336824</v>
       </c>
       <c r="N83">
-        <v>-118.8107977714286</v>
+        <v>-121.2051109714286</v>
       </c>
       <c r="O83">
-        <v>-26.13837550971429</v>
+        <v>-26.66512441371429</v>
       </c>
       <c r="P83">
-        <v>-92.6724222617143</v>
+        <v>-94.53998655771429</v>
       </c>
       <c r="Q83">
-        <v>-46.37242226171431</v>
+        <v>-48.23998655771429</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3331002319715737</v>
+        <v>0.3490613559699945</v>
       </c>
       <c r="T83">
-        <v>6.635109283408169</v>
+        <v>7.003726465819735</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08522398408567018</v>
+        <v>0.08418466720657665</v>
       </c>
       <c r="W83">
-        <v>0.215704184552599</v>
+        <v>0.2159492554726892</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3873817458439553</v>
+        <v>0.382657578211712</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2399094335622042</v>
+        <v>0.2418094335622042</v>
       </c>
       <c r="C84">
-        <v>-521.878256276161</v>
+        <v>-534.5733814864292</v>
       </c>
       <c r="D84">
-        <v>262.149743723839</v>
+        <v>259.6086185135708</v>
       </c>
       <c r="E84">
-        <v>441.128</v>
+        <v>451.282</v>
       </c>
       <c r="F84">
-        <v>832.628</v>
+        <v>842.782</v>
       </c>
       <c r="G84">
         <v>48.6</v>
@@ -8181,37 +8181,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M84">
-        <v>196.3336824</v>
+        <v>198.7279956</v>
       </c>
       <c r="N84">
-        <v>-121.2051109714286</v>
+        <v>-123.5994241714286</v>
       </c>
       <c r="O84">
-        <v>-26.66512441371429</v>
+        <v>-27.19187331771429</v>
       </c>
       <c r="P84">
-        <v>-94.53998655771429</v>
+        <v>-96.4075508537143</v>
       </c>
       <c r="Q84">
-        <v>-48.23998655771429</v>
+        <v>-50.1075508537143</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3490613559699945</v>
+        <v>0.3669002592623471</v>
       </c>
       <c r="T84">
-        <v>7.003726465819735</v>
+        <v>7.415710375573837</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08418466720657665</v>
+        <v>0.08317039410770223</v>
       </c>
       <c r="W84">
-        <v>0.2159492554726892</v>
+        <v>0.2161884210694038</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.382657578211712</v>
+        <v>0.378047245944101</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2418094335622042</v>
+        <v>0.2437094335622041</v>
       </c>
       <c r="C85">
-        <v>-534.5733814864292</v>
+        <v>-547.2197153095196</v>
       </c>
       <c r="D85">
-        <v>259.6086185135708</v>
+        <v>257.1162846904804</v>
       </c>
       <c r="E85">
-        <v>451.282</v>
+        <v>461.436</v>
       </c>
       <c r="F85">
-        <v>842.782</v>
+        <v>852.936</v>
       </c>
       <c r="G85">
         <v>48.6</v>
@@ -8263,37 +8263,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M85">
-        <v>198.7279956</v>
+        <v>201.1223088</v>
       </c>
       <c r="N85">
-        <v>-123.5994241714286</v>
+        <v>-125.9937373714286</v>
       </c>
       <c r="O85">
-        <v>-27.19187331771429</v>
+        <v>-27.71862222171429</v>
       </c>
       <c r="P85">
-        <v>-96.4075508537143</v>
+        <v>-98.2751151497143</v>
       </c>
       <c r="Q85">
-        <v>-50.1075508537143</v>
+        <v>-51.9751151497143</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3669002592623471</v>
+        <v>0.3869690254662438</v>
       </c>
       <c r="T85">
-        <v>7.415710375573837</v>
+        <v>7.879192274047203</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08317039410770223</v>
+        <v>0.08218027036832483</v>
       </c>
       <c r="W85">
-        <v>0.2161884210694038</v>
+        <v>0.216421892247149</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.378047245944101</v>
+        <v>0.3735466834923855</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2437094335622041</v>
+        <v>0.2456094335622042</v>
       </c>
       <c r="C86">
-        <v>-547.2197153095195</v>
+        <v>-559.818649626196</v>
       </c>
       <c r="D86">
-        <v>257.1162846904804</v>
+        <v>254.6713503738038</v>
       </c>
       <c r="E86">
-        <v>461.4359999999999</v>
+        <v>471.5899999999999</v>
       </c>
       <c r="F86">
-        <v>852.9359999999999</v>
+        <v>863.0899999999999</v>
       </c>
       <c r="G86">
         <v>48.6</v>
@@ -8345,37 +8345,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M86">
-        <v>201.1223088</v>
+        <v>203.516622</v>
       </c>
       <c r="N86">
-        <v>-125.9937373714286</v>
+        <v>-128.3880505714286</v>
       </c>
       <c r="O86">
-        <v>-27.71862222171428</v>
+        <v>-28.24537112571428</v>
       </c>
       <c r="P86">
-        <v>-98.27511514971427</v>
+        <v>-100.1426794457143</v>
       </c>
       <c r="Q86">
-        <v>-51.97511514971427</v>
+        <v>-53.84267944571427</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3869690254662436</v>
+        <v>0.4097136271639932</v>
       </c>
       <c r="T86">
-        <v>7.879192274047197</v>
+        <v>8.404471758983679</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08218027036832484</v>
+        <v>0.08121344365810924</v>
       </c>
       <c r="W86">
-        <v>0.216421892247149</v>
+        <v>0.2166498699854179</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3735466834923856</v>
+        <v>0.3691520166277693</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2456094335622042</v>
+        <v>0.2475094335622042</v>
       </c>
       <c r="C87">
-        <v>-559.818649626196</v>
+        <v>-572.3715238739937</v>
       </c>
       <c r="D87">
-        <v>254.6713503738038</v>
+        <v>252.2724761260062</v>
       </c>
       <c r="E87">
-        <v>471.5899999999999</v>
+        <v>481.7439999999999</v>
       </c>
       <c r="F87">
-        <v>863.0899999999999</v>
+        <v>873.2439999999999</v>
       </c>
       <c r="G87">
         <v>48.6</v>
@@ -8427,37 +8427,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M87">
-        <v>203.516622</v>
+        <v>205.9109352</v>
       </c>
       <c r="N87">
-        <v>-128.3880505714286</v>
+        <v>-130.7823637714285</v>
       </c>
       <c r="O87">
-        <v>-28.24537112571428</v>
+        <v>-28.77212002971428</v>
       </c>
       <c r="P87">
-        <v>-100.1426794457143</v>
+        <v>-102.0102437417143</v>
       </c>
       <c r="Q87">
-        <v>-53.84267944571427</v>
+        <v>-55.71024374171428</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4097136271639932</v>
+        <v>0.4357074576757071</v>
       </c>
       <c r="T87">
-        <v>8.404471758983679</v>
+        <v>9.004791170339656</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08121344365810924</v>
+        <v>0.08026910128999169</v>
       </c>
       <c r="W87">
-        <v>0.2166498699854179</v>
+        <v>0.21687254591582</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3691520166277693</v>
+        <v>0.3648595513181441</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2475094335622042</v>
+        <v>0.2494094335622042</v>
       </c>
       <c r="C88">
-        <v>-572.3715238739937</v>
+        <v>-584.8796274941142</v>
       </c>
       <c r="D88">
-        <v>252.2724761260062</v>
+        <v>249.9183725058859</v>
       </c>
       <c r="E88">
-        <v>481.7439999999999</v>
+        <v>491.898</v>
       </c>
       <c r="F88">
-        <v>873.2439999999999</v>
+        <v>883.398</v>
       </c>
       <c r="G88">
         <v>48.6</v>
@@ -8509,37 +8509,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M88">
-        <v>205.9109352</v>
+        <v>208.3052484</v>
       </c>
       <c r="N88">
-        <v>-130.7823637714285</v>
+        <v>-133.1766769714286</v>
       </c>
       <c r="O88">
-        <v>-28.77212002971428</v>
+        <v>-29.29886893371429</v>
       </c>
       <c r="P88">
-        <v>-102.0102437417143</v>
+        <v>-103.8778080377143</v>
       </c>
       <c r="Q88">
-        <v>-55.71024374171428</v>
+        <v>-57.57780803771429</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4357074576757071</v>
+        <v>0.4657003390353768</v>
       </c>
       <c r="T88">
-        <v>9.004791170339656</v>
+        <v>9.697467414211937</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08026910128999169</v>
+        <v>0.07934646794183087</v>
       </c>
       <c r="W88">
-        <v>0.21687254591582</v>
+        <v>0.2170901028593163</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3648595513181441</v>
+        <v>0.3606657633719584</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2494094335622042</v>
+        <v>0.2513094335622041</v>
       </c>
       <c r="C89">
-        <v>-584.8796274941142</v>
+        <v>-597.3442022425838</v>
       </c>
       <c r="D89">
-        <v>249.9183725058859</v>
+        <v>247.6077977574161</v>
       </c>
       <c r="E89">
-        <v>491.898</v>
+        <v>502.052</v>
       </c>
       <c r="F89">
-        <v>883.398</v>
+        <v>893.552</v>
       </c>
       <c r="G89">
         <v>48.6</v>
@@ -8591,37 +8591,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M89">
-        <v>208.3052484</v>
+        <v>210.6995616</v>
       </c>
       <c r="N89">
-        <v>-133.1766769714286</v>
+        <v>-135.5709901714286</v>
       </c>
       <c r="O89">
-        <v>-29.29886893371429</v>
+        <v>-29.82561783771429</v>
       </c>
       <c r="P89">
-        <v>-103.8778080377143</v>
+        <v>-105.7453723337143</v>
       </c>
       <c r="Q89">
-        <v>-57.57780803771429</v>
+        <v>-59.44537233371429</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4657003390353768</v>
+        <v>0.5006920339549915</v>
       </c>
       <c r="T89">
-        <v>9.697467414211937</v>
+        <v>10.5055896987296</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07934646794183087</v>
+        <v>0.07844480353340097</v>
       </c>
       <c r="W89">
-        <v>0.2170901028593163</v>
+        <v>0.217302715326824</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3606657633719584</v>
+        <v>0.3565672887881862</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2513094335622041</v>
+        <v>0.2532094335622042</v>
       </c>
       <c r="C90">
-        <v>-597.3442022425838</v>
+        <v>-609.7664443743865</v>
       </c>
       <c r="D90">
-        <v>247.6077977574161</v>
+        <v>245.3395556256135</v>
       </c>
       <c r="E90">
-        <v>502.052</v>
+        <v>512.206</v>
       </c>
       <c r="F90">
-        <v>893.552</v>
+        <v>903.706</v>
       </c>
       <c r="G90">
         <v>48.6</v>
@@ -8673,37 +8673,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M90">
-        <v>210.6995616</v>
+        <v>213.0938748</v>
       </c>
       <c r="N90">
-        <v>-135.5709901714286</v>
+        <v>-137.9653033714286</v>
       </c>
       <c r="O90">
-        <v>-29.82561783771429</v>
+        <v>-30.35236674171429</v>
       </c>
       <c r="P90">
-        <v>-105.7453723337143</v>
+        <v>-107.6129366297143</v>
       </c>
       <c r="Q90">
-        <v>-59.44537233371429</v>
+        <v>-61.31293662971429</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5006920339549915</v>
+        <v>0.5420458552236271</v>
       </c>
       <c r="T90">
-        <v>10.5055896987296</v>
+        <v>11.46064330770502</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07844480353340097</v>
+        <v>0.07756340124650883</v>
       </c>
       <c r="W90">
-        <v>0.217302715326824</v>
+        <v>0.2175105499860732</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3565672887881862</v>
+        <v>0.3525609147568582</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2532094335622042</v>
+        <v>0.2551094335622042</v>
       </c>
       <c r="C91">
-        <v>-609.7664443743865</v>
+        <v>-622.1475067086321</v>
       </c>
       <c r="D91">
-        <v>245.3395556256135</v>
+        <v>243.1124932913679</v>
       </c>
       <c r="E91">
-        <v>512.206</v>
+        <v>522.36</v>
       </c>
       <c r="F91">
-        <v>903.706</v>
+        <v>913.86</v>
       </c>
       <c r="G91">
         <v>48.6</v>
@@ -8755,37 +8755,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M91">
-        <v>213.0938748</v>
+        <v>215.488188</v>
       </c>
       <c r="N91">
-        <v>-137.9653033714286</v>
+        <v>-140.3596165714286</v>
       </c>
       <c r="O91">
-        <v>-30.35236674171429</v>
+        <v>-30.87911564571429</v>
       </c>
       <c r="P91">
-        <v>-107.6129366297143</v>
+        <v>-109.4805009257143</v>
       </c>
       <c r="Q91">
-        <v>-61.31293662971429</v>
+        <v>-63.1805009257143</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5420458552236271</v>
+        <v>0.59167044074599</v>
       </c>
       <c r="T91">
-        <v>11.46064330770502</v>
+        <v>12.60670763847552</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07756340124650883</v>
+        <v>0.07670158567710317</v>
       </c>
       <c r="W91">
-        <v>0.2175105499860732</v>
+        <v>0.2177137660973391</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3525609147568582</v>
+        <v>0.3486435712595598</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2551094335622042</v>
+        <v>0.2570094335622042</v>
       </c>
       <c r="C92">
-        <v>-622.1475067086321</v>
+        <v>-634.488500582263</v>
       </c>
       <c r="D92">
-        <v>243.1124932913679</v>
+        <v>240.925499417737</v>
       </c>
       <c r="E92">
-        <v>522.36</v>
+        <v>532.514</v>
       </c>
       <c r="F92">
-        <v>913.86</v>
+        <v>924.014</v>
       </c>
       <c r="G92">
         <v>48.6</v>
@@ -8837,37 +8837,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M92">
-        <v>215.488188</v>
+        <v>217.8825012</v>
       </c>
       <c r="N92">
-        <v>-140.3596165714286</v>
+        <v>-142.7539297714286</v>
       </c>
       <c r="O92">
-        <v>-30.87911564571429</v>
+        <v>-31.40586454971429</v>
       </c>
       <c r="P92">
-        <v>-109.4805009257143</v>
+        <v>-111.3480652217143</v>
       </c>
       <c r="Q92">
-        <v>-63.1805009257143</v>
+        <v>-65.04806522171428</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.59167044074599</v>
+        <v>0.6523227119399889</v>
       </c>
       <c r="T92">
-        <v>12.60670763847552</v>
+        <v>14.00745293163947</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07670158567710317</v>
+        <v>0.07585871110922292</v>
       </c>
       <c r="W92">
-        <v>0.2177137660973391</v>
+        <v>0.2179125159204452</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3486435712595598</v>
+        <v>0.3448123232237406</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2570094335622042</v>
+        <v>0.2589094335622042</v>
       </c>
       <c r="C93">
-        <v>-634.488500582263</v>
+        <v>-646.790497699247</v>
       </c>
       <c r="D93">
-        <v>240.925499417737</v>
+        <v>238.777502300753</v>
       </c>
       <c r="E93">
-        <v>532.514</v>
+        <v>542.668</v>
       </c>
       <c r="F93">
-        <v>924.014</v>
+        <v>934.168</v>
       </c>
       <c r="G93">
         <v>48.6</v>
@@ -8919,37 +8919,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M93">
-        <v>217.8825012</v>
+        <v>220.2768144</v>
       </c>
       <c r="N93">
-        <v>-142.7539297714286</v>
+        <v>-145.1482429714286</v>
       </c>
       <c r="O93">
-        <v>-31.40586454971429</v>
+        <v>-31.93261345371429</v>
       </c>
       <c r="P93">
-        <v>-111.3480652217143</v>
+        <v>-113.2156295177143</v>
       </c>
       <c r="Q93">
-        <v>-65.04806522171428</v>
+        <v>-66.91562951771429</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6523227119399889</v>
+        <v>0.7281380509324876</v>
       </c>
       <c r="T93">
-        <v>14.00745293163947</v>
+        <v>15.75838454809441</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07585871110922292</v>
+        <v>0.07503415990151398</v>
       </c>
       <c r="W93">
-        <v>0.2179125159204452</v>
+        <v>0.218106945095223</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3448123232237406</v>
+        <v>0.3410643631886998</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2589094335622042</v>
+        <v>0.2608094335622042</v>
       </c>
       <c r="C94">
-        <v>-646.790497699247</v>
+        <v>-659.0545318817246</v>
       </c>
       <c r="D94">
-        <v>238.777502300753</v>
+        <v>236.6674681182753</v>
       </c>
       <c r="E94">
-        <v>542.668</v>
+        <v>552.822</v>
       </c>
       <c r="F94">
-        <v>934.168</v>
+        <v>944.322</v>
       </c>
       <c r="G94">
         <v>48.6</v>
@@ -9001,37 +9001,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M94">
-        <v>220.2768144</v>
+        <v>222.6711276</v>
       </c>
       <c r="N94">
-        <v>-145.1482429714286</v>
+        <v>-147.5425561714286</v>
       </c>
       <c r="O94">
-        <v>-31.93261345371429</v>
+        <v>-32.45936235771428</v>
       </c>
       <c r="P94">
-        <v>-113.2156295177143</v>
+        <v>-115.0831938137143</v>
       </c>
       <c r="Q94">
-        <v>-66.91562951771429</v>
+        <v>-68.78319381371429</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7281380509324876</v>
+        <v>0.8256149153514145</v>
       </c>
       <c r="T94">
-        <v>15.75838454809441</v>
+        <v>18.00958234067932</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07503415990151398</v>
+        <v>0.07422734097784178</v>
       </c>
       <c r="W94">
-        <v>0.218106945095223</v>
+        <v>0.2182971929974249</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3410643631886998</v>
+        <v>0.3373970044447353</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2608094335622042</v>
+        <v>0.2627094335622042</v>
       </c>
       <c r="C95">
-        <v>-659.0545318817246</v>
+        <v>-671.2816007291235</v>
       </c>
       <c r="D95">
-        <v>236.6674681182753</v>
+        <v>234.5943992708765</v>
       </c>
       <c r="E95">
-        <v>552.822</v>
+        <v>562.976</v>
       </c>
       <c r="F95">
-        <v>944.322</v>
+        <v>954.476</v>
       </c>
       <c r="G95">
         <v>48.6</v>
@@ -9083,37 +9083,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M95">
-        <v>222.6711276</v>
+        <v>225.0654408</v>
       </c>
       <c r="N95">
-        <v>-147.5425561714286</v>
+        <v>-149.9368693714286</v>
       </c>
       <c r="O95">
-        <v>-32.45936235771428</v>
+        <v>-32.98611126171429</v>
       </c>
       <c r="P95">
-        <v>-115.0831938137143</v>
+        <v>-116.9507581097143</v>
       </c>
       <c r="Q95">
-        <v>-68.78319381371429</v>
+        <v>-70.65075810971429</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8256149153514145</v>
+        <v>0.955584067909984</v>
       </c>
       <c r="T95">
-        <v>18.00958234067932</v>
+        <v>21.01117939745922</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07422734097784178</v>
+        <v>0.07343768841424771</v>
       </c>
       <c r="W95">
-        <v>0.2182971929974249</v>
+        <v>0.2184833930719204</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3373970044447353</v>
+        <v>0.3338076746102169</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2627094335622042</v>
+        <v>0.2646094335622042</v>
       </c>
       <c r="C96">
-        <v>-671.2816007291235</v>
+        <v>-683.4726671908305</v>
       </c>
       <c r="D96">
-        <v>234.5943992708765</v>
+        <v>232.5573328091695</v>
       </c>
       <c r="E96">
-        <v>562.976</v>
+        <v>573.13</v>
       </c>
       <c r="F96">
-        <v>954.476</v>
+        <v>964.63</v>
       </c>
       <c r="G96">
         <v>48.6</v>
@@ -9165,37 +9165,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M96">
-        <v>225.0654408</v>
+        <v>227.459754</v>
       </c>
       <c r="N96">
-        <v>-149.9368693714286</v>
+        <v>-152.3311825714286</v>
       </c>
       <c r="O96">
-        <v>-32.98611126171429</v>
+        <v>-33.51286016571429</v>
       </c>
       <c r="P96">
-        <v>-116.9507581097143</v>
+        <v>-118.8183224057143</v>
       </c>
       <c r="Q96">
-        <v>-70.65075810971429</v>
+        <v>-72.51832240571429</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.955584067909984</v>
+        <v>1.137540881491981</v>
       </c>
       <c r="T96">
-        <v>21.01117939745922</v>
+        <v>25.21341527695107</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07343768841424771</v>
+        <v>0.07266466011515037</v>
       </c>
       <c r="W96">
-        <v>0.2184833930719204</v>
+        <v>0.2186656731448476</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3338076746102169</v>
+        <v>0.3302939096143198</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2646094335622042</v>
+        <v>0.2665094335622042</v>
       </c>
       <c r="C97">
-        <v>-683.4726671908305</v>
+        <v>-695.6286610576351</v>
       </c>
       <c r="D97">
-        <v>232.5573328091695</v>
+        <v>230.555338942365</v>
       </c>
       <c r="E97">
-        <v>573.13</v>
+        <v>583.2840000000001</v>
       </c>
       <c r="F97">
-        <v>964.63</v>
+        <v>974.7840000000001</v>
       </c>
       <c r="G97">
         <v>48.6</v>
@@ -9247,37 +9247,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M97">
-        <v>227.459754</v>
+        <v>229.8540672</v>
       </c>
       <c r="N97">
-        <v>-152.3311825714286</v>
+        <v>-154.7254957714286</v>
       </c>
       <c r="O97">
-        <v>-33.51286016571429</v>
+        <v>-34.0396090697143</v>
       </c>
       <c r="P97">
-        <v>-118.8183224057143</v>
+        <v>-120.6858867017143</v>
       </c>
       <c r="Q97">
-        <v>-72.51832240571429</v>
+        <v>-74.38588670171431</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.137540881491981</v>
+        <v>1.410476101864977</v>
       </c>
       <c r="T97">
-        <v>25.21341527695107</v>
+        <v>31.51676909618886</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07266466011515037</v>
+        <v>0.07190773657228421</v>
       </c>
       <c r="W97">
-        <v>0.2186656731448476</v>
+        <v>0.2188441557162554</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3302939096143198</v>
+        <v>0.3268533480558373</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2665094335622041</v>
+        <v>0.2684094335622041</v>
       </c>
       <c r="C98">
-        <v>-695.6286610576349</v>
+        <v>-707.7504803767928</v>
       </c>
       <c r="D98">
-        <v>230.5553389423651</v>
+        <v>228.5875196232072</v>
       </c>
       <c r="E98">
-        <v>583.284</v>
+        <v>593.438</v>
       </c>
       <c r="F98">
-        <v>974.784</v>
+        <v>984.938</v>
       </c>
       <c r="G98">
         <v>48.6</v>
@@ -9329,37 +9329,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M98">
-        <v>229.8540672</v>
+        <v>232.2483804</v>
       </c>
       <c r="N98">
-        <v>-154.7254957714286</v>
+        <v>-157.1198089714286</v>
       </c>
       <c r="O98">
-        <v>-34.03960906971429</v>
+        <v>-34.56635797371428</v>
       </c>
       <c r="P98">
-        <v>-120.6858867017143</v>
+        <v>-122.5534509977143</v>
       </c>
       <c r="Q98">
-        <v>-74.38588670171428</v>
+        <v>-76.2534509977143</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.410476101864974</v>
+        <v>1.865368135819965</v>
       </c>
       <c r="T98">
-        <v>31.51676909618877</v>
+        <v>42.02235879491836</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07190773657228422</v>
+        <v>0.07116641970040501</v>
       </c>
       <c r="W98">
-        <v>0.2188441557162554</v>
+        <v>0.2190189582346445</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3268533480558373</v>
+        <v>0.3234837259109319</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2684094335622041</v>
+        <v>0.2703094335622042</v>
       </c>
       <c r="C99">
-        <v>-707.7504803767928</v>
+        <v>-719.8389927952376</v>
       </c>
       <c r="D99">
-        <v>228.5875196232072</v>
+        <v>226.6530072047624</v>
       </c>
       <c r="E99">
-        <v>593.438</v>
+        <v>603.592</v>
       </c>
       <c r="F99">
-        <v>984.938</v>
+        <v>995.092</v>
       </c>
       <c r="G99">
         <v>48.6</v>
@@ -9411,37 +9411,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M99">
-        <v>232.2483804</v>
+        <v>234.6426936</v>
       </c>
       <c r="N99">
-        <v>-157.1198089714286</v>
+        <v>-159.5141221714286</v>
       </c>
       <c r="O99">
-        <v>-34.56635797371428</v>
+        <v>-35.09310687771428</v>
       </c>
       <c r="P99">
-        <v>-122.5534509977143</v>
+        <v>-124.4210152937143</v>
       </c>
       <c r="Q99">
-        <v>-76.2534509977143</v>
+        <v>-78.12101529371428</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.865368135819965</v>
+        <v>2.775152203729947</v>
       </c>
       <c r="T99">
-        <v>42.02235879491836</v>
+        <v>63.03353819237754</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07116641970040501</v>
+        <v>0.07044023174427842</v>
       </c>
       <c r="W99">
-        <v>0.2190189582346445</v>
+        <v>0.2191901933546992</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3234837259109319</v>
+        <v>0.3201828715649019</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2703094335622042</v>
+        <v>0.2722094335622042</v>
       </c>
       <c r="C100">
-        <v>-719.8389927952376</v>
+        <v>-731.8950368351593</v>
       </c>
       <c r="D100">
-        <v>226.6530072047624</v>
+        <v>224.7509631648407</v>
       </c>
       <c r="E100">
-        <v>603.592</v>
+        <v>613.746</v>
       </c>
       <c r="F100">
-        <v>995.092</v>
+        <v>1005.246</v>
       </c>
       <c r="G100">
         <v>48.6</v>
@@ -9493,37 +9493,37 @@
         <v>75.12857142857143</v>
       </c>
       <c r="M100">
-        <v>234.6426936</v>
+        <v>237.0370068</v>
       </c>
       <c r="N100">
-        <v>-159.5141221714286</v>
+        <v>-161.9084353714286</v>
       </c>
       <c r="O100">
-        <v>-35.09310687771428</v>
+        <v>-35.61985578171429</v>
       </c>
       <c r="P100">
-        <v>-124.4210152937143</v>
+        <v>-126.2885795897143</v>
       </c>
       <c r="Q100">
-        <v>-78.12101529371428</v>
+        <v>-79.98857958971429</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.775152203729947</v>
+        <v>5.504504407459894</v>
       </c>
       <c r="T100">
-        <v>63.03353819237754</v>
+        <v>126.0670763847551</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07044023174427842</v>
+        <v>0.06972871425191197</v>
       </c>
       <c r="W100">
-        <v>0.2191901933546992</v>
+        <v>0.2193579691793992</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3201828715649019</v>
+        <v>0.3169487011450545</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2722094335622042</v>
-      </c>
-      <c r="C101">
-        <v>-731.8950368351593</v>
-      </c>
-      <c r="D101">
-        <v>224.7509631648407</v>
-      </c>
-      <c r="E101">
-        <v>613.746</v>
-      </c>
-      <c r="F101">
-        <v>1005.246</v>
-      </c>
-      <c r="G101">
-        <v>48.6</v>
-      </c>
-      <c r="H101">
-        <v>623.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>121.4285714285714</v>
-      </c>
-      <c r="K101">
-        <v>46.3</v>
-      </c>
-      <c r="L101">
-        <v>75.12857142857143</v>
-      </c>
-      <c r="M101">
-        <v>237.0370068</v>
-      </c>
-      <c r="N101">
-        <v>-161.9084353714286</v>
-      </c>
-      <c r="O101">
-        <v>-35.61985578171429</v>
-      </c>
-      <c r="P101">
-        <v>-126.2885795897143</v>
-      </c>
-      <c r="Q101">
-        <v>-79.98857958971429</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.504504407459894</v>
-      </c>
-      <c r="T101">
-        <v>126.0670763847551</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06972871425191197</v>
-      </c>
-      <c r="W101">
-        <v>0.2193579691793992</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3169487011450545</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
